--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -654,20 +654,20 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Raleigh</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>75</v>
+        <v>73.8</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -685,20 +685,20 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -747,20 +747,20 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>69.3</v>
+        <v>69.7</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -809,32 +809,32 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>66</v>
+        <v>70.5</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -853,69 +853,69 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>63.8</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Very Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>61.7</v>
+        <v>63</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -933,16 +933,16 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -963,176 +963,176 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="D12" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Las Vegas</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="A13" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Nashville</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="A14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Orlando-Kissimmee-Sanford</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="A15" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Baltimore-Columbia-Towson</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Orlando-Kissimmee-Sanford</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Orlando</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A16" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>54.7</v>
+        <v>53.1</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1212,16 +1212,16 @@
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>52.3</v>
+        <v>51.7</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1243,20 +1243,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="F22" s="11" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1305,20 +1305,20 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1336,16 +1336,16 @@
     </row>
     <row r="24">
       <c r="A24" s="14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -1367,16 +1367,16 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
@@ -1398,16 +1398,16 @@
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1429,20 +1429,20 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>47.3</v>
+        <v>48.3</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1460,20 +1460,20 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>47.1</v>
+        <v>45.8</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1491,20 +1491,20 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1522,20 +1522,20 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1553,16 +1553,16 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1583,110 +1583,110 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Boston-Cambridge-Newton</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="n">
+      <c r="A32" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Virginia Beach</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>Denver-Aurora-Centennial</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Providence-Warwick</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1708,16 +1708,16 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1739,20 +1739,20 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1770,20 +1770,20 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>39.5</v>
+        <v>40.4</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>39.4</v>
+        <v>39.8</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1832,78 +1832,78 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Milwaukee-Waukesha</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="n">
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F40" s="17" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
+      <c r="F41" s="17" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B41" s="21" t="inlineStr">
-        <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="G41" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D42" s="22" t="n">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -1925,16 +1925,16 @@
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -1955,114 +1955,114 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="n">
+      <c r="A44" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D44" s="25" t="n">
+      <c r="D44" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Grand Rapids</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="23" t="n">
-        <v>49</v>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>Grand Rapids</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="23" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="F47" s="23" t="n">
-        <v>28.5</v>
+        <v>30.4</v>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
@@ -2080,20 +2080,20 @@
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>27.7</v>
+        <v>28.6</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2111,16 +2111,16 @@
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="F49" s="23" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
     </row>
     <row r="50">
       <c r="A50" s="23" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="F50" s="23" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
@@ -2173,16 +2173,16 @@
     </row>
     <row r="51">
       <c r="A51" s="23" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="F51" s="23" t="n">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
@@ -2298,71 +2298,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="B2" s="26" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="27" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D2" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="E2" s="29" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="G2" s="27" t="n">
+        <v>98</v>
+      </c>
+      <c r="H2" s="30" t="n"/>
+      <c r="I2" s="27" t="n">
+        <v>98</v>
+      </c>
+      <c r="J2" s="28" t="n">
         <v>54</v>
       </c>
-      <c r="E2" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>88</v>
-      </c>
-      <c r="G2" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="J2" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="K2" s="27" t="n">
-        <v>98</v>
+      <c r="K2" s="28" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B3" s="26" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="D3" s="28" t="n">
-        <v>68</v>
+        <v>82</v>
+      </c>
+      <c r="D3" s="27" t="n">
+        <v>70</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>48</v>
       </c>
       <c r="F3" s="27" t="n">
-        <v>73</v>
-      </c>
-      <c r="G3" s="27" t="n">
-        <v>98</v>
+        <v>96</v>
+      </c>
+      <c r="G3" s="28" t="n">
+        <v>54</v>
       </c>
       <c r="H3" s="30" t="n"/>
       <c r="I3" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="J3" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="K3" s="28" t="n">
-        <v>52</v>
+        <v>78</v>
+      </c>
+      <c r="J3" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="K3" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="B4" s="26" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>72</v>
@@ -2381,17 +2381,17 @@
         <v>86</v>
       </c>
       <c r="E4" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>55</v>
+        <v>64</v>
+      </c>
+      <c r="F4" s="29" t="n">
+        <v>37</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H4" s="30" t="n"/>
       <c r="I4" s="27" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>88</v>
@@ -2403,36 +2403,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>54</v>
+      </c>
+      <c r="E5" s="27" t="n">
         <v>98</v>
       </c>
-      <c r="D5" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>72</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>29</v>
+      <c r="F5" s="27" t="n">
+        <v>90</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H5" s="30" t="n"/>
-      <c r="I5" s="27" t="n">
-        <v>88</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>38</v>
-      </c>
-      <c r="K5" s="29" t="n">
-        <v>4</v>
+      <c r="I5" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>78</v>
@@ -2451,17 +2451,17 @@
         <v>66</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>80</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H6" s="30" t="n"/>
-      <c r="I6" s="28" t="n">
-        <v>66</v>
+      <c r="I6" s="27" t="n">
+        <v>70</v>
       </c>
       <c r="J6" s="29" t="n">
         <v>44</v>
@@ -2473,36 +2473,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="E7" s="29" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>74</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" s="30" t="n"/>
+      <c r="I7" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="J7" s="29" t="n">
         <v>38</v>
       </c>
-      <c r="F7" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="H7" s="30" t="n"/>
-      <c r="I7" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>70</v>
-      </c>
       <c r="K7" s="29" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="B8" s="26" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>80</v>
@@ -2521,17 +2521,17 @@
         <v>40</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>73</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H8" s="30" t="n"/>
       <c r="I8" s="27" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J8" s="29" t="n">
         <v>12</v>
@@ -2543,106 +2543,106 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>63</v>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>44</v>
+        <v>64</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>72</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>39</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>60</v>
       </c>
       <c r="H9" s="30" t="n"/>
       <c r="I9" s="27" t="n">
         <v>84</v>
       </c>
-      <c r="J9" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <v>16</v>
+      <c r="J9" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B10" s="26" t="n">
-        <v>62</v>
-      </c>
-      <c r="C10" s="27" t="n">
-        <v>72</v>
+        <v>63</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>44</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>88</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>47</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>50</v>
+        <v>78</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>94</v>
       </c>
       <c r="H10" s="30" t="n"/>
       <c r="I10" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="J10" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="K10" s="27" t="n">
-        <v>84</v>
+        <v>80</v>
+      </c>
+      <c r="J10" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="29" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B11" s="26" t="n">
         <v>61</v>
       </c>
-      <c r="C11" s="27" t="n">
-        <v>90</v>
+      <c r="C11" s="29" t="n">
+        <v>30</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>58</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>57</v>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>88</v>
       </c>
       <c r="H11" s="30" t="n"/>
-      <c r="I11" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="J11" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>72</v>
+      <c r="I11" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="K11" s="28" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="B12" s="26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="29" t="n">
         <v>28</v>
@@ -2661,17 +2661,17 @@
         <v>76</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F12" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="G12" s="27" t="n">
         <v>94</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>92</v>
       </c>
       <c r="H12" s="30" t="n"/>
       <c r="I12" s="27" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J12" s="29" t="n">
         <v>24</v>
@@ -2683,211 +2683,211 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B13" s="26" t="n">
-        <v>60</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>90</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>45</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="H13" s="30" t="n"/>
-      <c r="I13" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="K13" s="28" t="n">
-        <v>50</v>
+      <c r="I13" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B14" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="C14" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>51</v>
+      <c r="E14" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>71</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H14" s="30" t="n"/>
       <c r="I14" s="27" t="n">
         <v>72</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="K14" s="29" t="n">
         <v>28</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>60</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>34</v>
+        <v>54</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>56</v>
       </c>
       <c r="E15" s="27" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G15" s="29" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H15" s="30" t="n"/>
-      <c r="I15" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="J15" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>8</v>
+      <c r="I15" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B16" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="C16" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="E16" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>90</v>
+        <v>54</v>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H16" s="30" t="n"/>
       <c r="I16" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="J16" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="K16" s="28" t="n">
-        <v>64</v>
+        <v>94</v>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>98</v>
+      </c>
+      <c r="K16" s="29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B17" s="26" t="n">
-        <v>55</v>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>8</v>
+        <v>38</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>76</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H17" s="30" t="n"/>
-      <c r="I17" s="27" t="n">
-        <v>90</v>
+      <c r="I17" s="28" t="n">
+        <v>66</v>
       </c>
       <c r="J17" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B18" s="26" t="n">
         <v>53</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="E18" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="D18" s="27" t="n">
-        <v>72</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>68</v>
+      <c r="F18" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>82</v>
       </c>
       <c r="H18" s="30" t="n"/>
       <c r="I18" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="J18" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>18</v>
+      <c r="J18" s="28" t="n">
+        <v>52</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="19">
@@ -2906,13 +2906,13 @@
         <v>82</v>
       </c>
       <c r="E19" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="F19" s="28" t="n">
-        <v>67</v>
+        <v>36</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>78</v>
       </c>
       <c r="G19" s="29" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H19" s="30" t="n"/>
       <c r="I19" s="29" t="n">
@@ -2928,392 +2928,392 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B20" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="C20" s="29" t="n">
-        <v>8</v>
+      <c r="C20" s="27" t="n">
+        <v>96</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>38</v>
-      </c>
-      <c r="E20" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>41</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>74</v>
+        <v>22</v>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>67</v>
+      </c>
+      <c r="G20" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="H20" s="30" t="n"/>
-      <c r="I20" s="28" t="n">
-        <v>58</v>
-      </c>
-      <c r="J20" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="K20" s="28" t="n">
-        <v>62</v>
+      <c r="I20" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="J20" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B21" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="C21" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>52</v>
+      </c>
+      <c r="F21" s="28" t="n">
         <v>51</v>
       </c>
-      <c r="C21" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="E21" s="27" t="n">
+      <c r="G21" s="27" t="n">
         <v>78</v>
       </c>
-      <c r="F21" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>82</v>
-      </c>
       <c r="H21" s="30" t="n"/>
-      <c r="I21" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="J21" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="K21" s="27" t="n">
-        <v>76</v>
+      <c r="I21" s="29" t="n">
+        <v>46</v>
+      </c>
+      <c r="J21" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="K21" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B22" s="26" t="n">
         <v>51</v>
       </c>
       <c r="C22" s="28" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D22" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="E22" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="G22" s="29" t="n">
-        <v>28</v>
+        <v>52</v>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>96</v>
+      </c>
+      <c r="F22" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H22" s="30" t="n"/>
       <c r="I22" s="29" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="K22" s="27" t="n">
-        <v>94</v>
+        <v>6</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B23" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="C23" s="27" t="n">
-        <v>96</v>
+        <v>51</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>56</v>
       </c>
       <c r="D23" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="E23" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G23" s="29" t="n">
         <v>46</v>
       </c>
-      <c r="F23" s="28" t="n">
-        <v>59</v>
-      </c>
-      <c r="G23" s="29" t="n">
-        <v>14</v>
-      </c>
       <c r="H23" s="30" t="n"/>
-      <c r="I23" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="J23" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" s="27" t="n">
-        <v>86</v>
+      <c r="I23" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="J23" s="27" t="n">
+        <v>82</v>
+      </c>
+      <c r="K23" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B24" s="26" t="n">
         <v>49</v>
       </c>
       <c r="C24" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="D24" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="28" t="n">
-        <v>64</v>
-      </c>
       <c r="E24" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="29" t="n">
+        <v>44</v>
       </c>
       <c r="H24" s="30" t="n"/>
-      <c r="I24" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="J24" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="K24" s="28" t="n">
-        <v>56</v>
+      <c r="I24" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="K24" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B25" s="26" t="n">
         <v>49</v>
       </c>
       <c r="C25" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="28" t="n">
         <v>60</v>
-      </c>
-      <c r="D25" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="E25" s="27" t="n">
-        <v>94</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>31</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>70</v>
       </c>
       <c r="H25" s="30" t="n"/>
       <c r="I25" s="29" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K25" s="28" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B26" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="C26" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" s="27" t="n">
-        <v>76</v>
+      <c r="C26" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="G26" s="29" t="n">
-        <v>32</v>
+        <v>82</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>84</v>
       </c>
       <c r="H26" s="30" t="n"/>
-      <c r="I26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="K26" s="27" t="n">
-        <v>90</v>
+      <c r="I26" s="27" t="n">
+        <v>74</v>
+      </c>
+      <c r="J26" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="K26" s="28" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B27" s="26" t="n">
-        <v>47</v>
-      </c>
-      <c r="C27" s="29" t="n">
         <v>48</v>
       </c>
+      <c r="C27" s="28" t="n">
+        <v>60</v>
+      </c>
       <c r="D27" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="E27" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="F27" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" s="28" t="n">
-        <v>54</v>
+        <v>6</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>69</v>
+      </c>
+      <c r="G27" s="29" t="n">
+        <v>32</v>
       </c>
       <c r="H27" s="30" t="n"/>
-      <c r="I27" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="J27" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="K27" s="29" t="n">
-        <v>28</v>
+      <c r="I27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="K27" s="27" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B28" s="26" t="n">
-        <v>47</v>
-      </c>
-      <c r="C28" s="28" t="n">
-        <v>66</v>
+        <v>46</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>72</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E28" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="G28" s="28" t="n">
-        <v>64</v>
+        <v>22</v>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>72</v>
       </c>
       <c r="H28" s="30" t="n"/>
       <c r="I28" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="J28" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="K28" s="28" t="n">
-        <v>66</v>
+        <v>34</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="K28" s="29" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D29" s="29" t="n">
-        <v>44</v>
+        <v>20</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>58</v>
       </c>
       <c r="E29" s="28" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>71</v>
-      </c>
-      <c r="G29" s="29" t="n">
-        <v>6</v>
+        <v>92</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>76</v>
       </c>
       <c r="H29" s="30" t="n"/>
       <c r="I29" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="J29" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="K29" s="27" t="n">
-        <v>74</v>
+        <v>28</v>
+      </c>
+      <c r="J29" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="K29" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>46</v>
-      </c>
-      <c r="C30" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="D30" s="27" t="n">
+        <v>98</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" s="28" t="n">
         <v>56</v>
-      </c>
-      <c r="D30" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="E30" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="G30" s="28" t="n">
-        <v>52</v>
       </c>
       <c r="H30" s="30" t="n"/>
       <c r="I30" s="29" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J30" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="K30" s="30" t="n">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="K30" s="27" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B31" s="26" t="n">
@@ -3323,268 +3323,268 @@
         <v>48</v>
       </c>
       <c r="D31" s="29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E31" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="G31" s="29" t="n">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="F31" s="28" t="n">
+        <v>63</v>
+      </c>
+      <c r="G31" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H31" s="30" t="n"/>
       <c r="I31" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="J31" s="27" t="n">
-        <v>86</v>
+        <v>68</v>
+      </c>
+      <c r="J31" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="K31" s="29" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D32" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="C32" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="D32" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="E32" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="F32" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="G32" s="28" t="n">
+      <c r="E32" s="28" t="n">
         <v>58</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="H32" s="30" t="n"/>
       <c r="I32" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="J32" s="27" t="n">
-        <v>94</v>
+        <v>42</v>
+      </c>
+      <c r="J32" s="28" t="n">
+        <v>68</v>
       </c>
       <c r="K32" s="27" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B33" s="26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" s="29" t="n">
         <v>48</v>
       </c>
       <c r="D33" s="29" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E33" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="F33" s="28" t="n">
-        <v>65</v>
-      </c>
-      <c r="G33" s="28" t="n">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="F33" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <v>48</v>
       </c>
       <c r="H33" s="30" t="n"/>
       <c r="I33" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="J33" s="29" t="n">
-        <v>20</v>
+        <v>64</v>
+      </c>
+      <c r="J33" s="27" t="n">
+        <v>86</v>
       </c>
       <c r="K33" s="29" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B34" s="26" t="n">
         <v>44</v>
       </c>
       <c r="C34" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="D34" s="27" t="n">
+        <v>46</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="E34" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>47</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="H34" s="30" t="n"/>
+      <c r="I34" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="J34" s="27" t="n">
         <v>92</v>
       </c>
-      <c r="E34" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="F34" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="H34" s="30" t="n"/>
-      <c r="I34" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="J34" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="K34" s="28" t="n">
-        <v>68</v>
+      <c r="K34" s="29" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B35" s="26" t="n">
         <v>43</v>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="F35" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="E35" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="F35" s="29" t="n">
-        <v>33</v>
-      </c>
-      <c r="G35" s="29" t="n">
-        <v>36</v>
+      <c r="G35" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H35" s="30" t="n"/>
-      <c r="I35" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="J35" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="K35" s="29" t="n">
-        <v>28</v>
+      <c r="I35" s="28" t="n">
+        <v>54</v>
+      </c>
+      <c r="J35" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="K35" s="28" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B36" s="26" t="n">
         <v>42</v>
       </c>
       <c r="C36" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="F36" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="D36" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="F36" s="28" t="n">
-        <v>53</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>84</v>
+      <c r="G36" s="28" t="n">
+        <v>52</v>
       </c>
       <c r="H36" s="30" t="n"/>
-      <c r="I36" s="27" t="n">
-        <v>82</v>
+      <c r="I36" s="28" t="n">
+        <v>52</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="K36" s="28" t="n">
-        <v>60</v>
+        <v>4</v>
+      </c>
+      <c r="K36" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B37" s="26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="29" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D37" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="E37" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="F37" s="28" t="n">
+        <v>53</v>
+      </c>
+      <c r="G37" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="F37" s="29" t="n">
-        <v>37</v>
-      </c>
-      <c r="G37" s="29" t="n">
-        <v>26</v>
-      </c>
       <c r="H37" s="30" t="n"/>
-      <c r="I37" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="K37" s="29" t="n">
-        <v>12</v>
+      <c r="I37" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="J37" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="K37" s="28" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C38" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="D38" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>59</v>
+      </c>
+      <c r="G38" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="H38" s="30" t="n"/>
+      <c r="I38" s="28" t="n">
         <v>58</v>
       </c>
-      <c r="E38" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="H38" s="30" t="n"/>
-      <c r="I38" s="29" t="n">
-        <v>16</v>
-      </c>
       <c r="J38" s="27" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K38" s="29" t="n">
         <v>28</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="B39" s="26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C39" s="29" t="n">
         <v>38</v>
@@ -3606,17 +3606,17 @@
         <v>42</v>
       </c>
       <c r="E39" s="27" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G39" s="29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H39" s="30" t="n"/>
       <c r="I39" s="29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39" s="28" t="n">
         <v>64</v>
@@ -3628,141 +3628,141 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B40" s="26" t="n">
-        <v>39</v>
-      </c>
-      <c r="C40" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="D40" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="E40" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="F40" s="29" t="n">
-        <v>14</v>
+        <v>40</v>
+      </c>
+      <c r="C40" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>98</v>
       </c>
       <c r="G40" s="29" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H40" s="30" t="n"/>
       <c r="I40" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="J40" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K40" s="27" t="n">
-        <v>92</v>
+        <v>4</v>
+      </c>
+      <c r="J40" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="K40" s="29" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B41" s="26" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C41" s="29" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D41" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="E41" s="27" t="n">
-        <v>92</v>
+        <v>10</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>24</v>
       </c>
       <c r="F41" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="G41" s="28" t="n">
-        <v>60</v>
+        <v>27</v>
+      </c>
+      <c r="G41" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="H41" s="30" t="n"/>
-      <c r="I41" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="J41" s="29" t="n">
-        <v>4</v>
+      <c r="I41" s="28" t="n">
+        <v>62</v>
+      </c>
+      <c r="J41" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="K41" s="29" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B42" s="26" t="n">
         <v>36</v>
       </c>
-      <c r="C42" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D42" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="E42" s="27" t="n">
-        <v>88</v>
+      <c r="C42" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="D42" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>6</v>
       </c>
       <c r="F42" s="29" t="n">
-        <v>35</v>
-      </c>
-      <c r="G42" s="30" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G42" s="29" t="n">
+        <v>30</v>
       </c>
       <c r="H42" s="30" t="n"/>
       <c r="I42" s="29" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="K42" s="28" t="n">
-        <v>54</v>
+        <v>30</v>
+      </c>
+      <c r="K42" s="27" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B43" s="26" t="n">
         <v>35</v>
       </c>
       <c r="C43" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="E43" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="F43" s="29" t="n">
+        <v>29</v>
+      </c>
+      <c r="G43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="30" t="n"/>
+      <c r="I43" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="J43" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="D43" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="E43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="29" t="n">
-        <v>43</v>
-      </c>
-      <c r="G43" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="H43" s="30" t="n"/>
-      <c r="I43" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="J43" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="K43" s="29" t="n">
-        <v>28</v>
+      <c r="K43" s="28" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="44">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="B44" s="26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C44" s="27" t="n">
         <v>88</v>
@@ -3781,17 +3781,17 @@
         <v>28</v>
       </c>
       <c r="E44" s="29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F44" s="29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G44" s="29" t="n">
         <v>14</v>
       </c>
       <c r="H44" s="30" t="n"/>
       <c r="I44" s="29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J44" s="29" t="n">
         <v>48</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="B45" s="26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C45" s="28" t="n">
         <v>68</v>
@@ -3816,17 +3816,17 @@
         <v>0</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F45" s="29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G45" s="29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H45" s="30" t="n"/>
       <c r="I45" s="29" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J45" s="29" t="n">
         <v>46</v>
@@ -3838,211 +3838,211 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B46" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="C46" s="28" t="n">
-        <v>54</v>
+        <v>32</v>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="D46" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="E46" s="29" t="n">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="E46" s="28" t="n">
+        <v>66</v>
       </c>
       <c r="F46" s="29" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G46" s="29" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H46" s="30" t="n"/>
       <c r="I46" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" s="28" t="n">
-        <v>62</v>
+        <v>38</v>
+      </c>
+      <c r="J46" s="29" t="n">
+        <v>40</v>
       </c>
       <c r="K46" s="29" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B47" s="26" t="n">
-        <v>29</v>
-      </c>
-      <c r="C47" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" s="28" t="n">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="C47" s="28" t="n">
+        <v>54</v>
+      </c>
+      <c r="D47" s="29" t="n">
+        <v>32</v>
       </c>
       <c r="E47" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>69</v>
-      </c>
-      <c r="G47" s="28" t="n">
-        <v>56</v>
+        <v>30</v>
+      </c>
+      <c r="F47" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="G47" s="29" t="n">
+        <v>22</v>
       </c>
       <c r="H47" s="30" t="n"/>
       <c r="I47" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="J47" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="K47" s="27" t="n">
-        <v>78</v>
+        <v>8</v>
+      </c>
+      <c r="J47" s="28" t="n">
+        <v>62</v>
+      </c>
+      <c r="K47" s="29" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B48" s="26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C48" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="D48" s="29" t="n">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="D48" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="E48" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="F48" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="G48" s="29" t="n">
-        <v>10</v>
+      <c r="F48" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="G48" s="28" t="n">
+        <v>58</v>
       </c>
       <c r="H48" s="30" t="n"/>
       <c r="I48" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="J48" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="K48" s="29" t="n">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="J48" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="K48" s="27" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B49" s="26" t="n">
         <v>28</v>
       </c>
       <c r="C49" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="D49" s="28" t="n">
-        <v>62</v>
+        <v>22</v>
+      </c>
+      <c r="D49" s="29" t="n">
+        <v>4</v>
       </c>
       <c r="E49" s="29" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F49" s="29" t="n">
-        <v>39</v>
-      </c>
-      <c r="G49" s="29" t="n">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="G49" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="H49" s="30" t="n"/>
-      <c r="I49" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="K49" s="27" t="n">
-        <v>94</v>
+      <c r="I49" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="29" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B50" s="26" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="D50" s="29" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D50" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="E50" s="29" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F50" s="29" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G50" s="29" t="n">
         <v>38</v>
       </c>
       <c r="H50" s="30" t="n"/>
       <c r="I50" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="J50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="29" t="n">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="J50" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="K50" s="27" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B51" s="26" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="D51" s="28" t="n">
+        <v>62</v>
+      </c>
+      <c r="E51" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="G51" s="29" t="n">
         <v>2</v>
-      </c>
-      <c r="D51" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="E51" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="F51" s="29" t="n">
-        <v>27</v>
-      </c>
-      <c r="G51" s="29" t="n">
-        <v>40</v>
       </c>
       <c r="H51" s="30" t="n"/>
       <c r="I51" s="29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J51" s="29" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K51" s="27" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4144,87 +4144,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>75 (A+)</t>
+          <t>74 (A+)</t>
         </is>
       </c>
       <c r="C2" s="30" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D2" s="30" t="n">
-        <v>-0.21</v>
+        <v>0.48</v>
       </c>
       <c r="E2" s="30" t="n">
-        <v>7.22</v>
+        <v>3.16</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="G2" s="30" t="n">
-        <v>2.28</v>
+        <v>4.54</v>
       </c>
       <c r="H2" s="30" t="n"/>
       <c r="I2" s="30" t="n">
-        <v>0.97</v>
+        <v>2.23</v>
       </c>
       <c r="J2" s="30" t="n">
-        <v>24.76</v>
+        <v>4.15</v>
       </c>
       <c r="K2" s="30" t="n">
-        <v>8.35</v>
+        <v>7.05</v>
       </c>
       <c r="L2" s="30" t="n">
-        <v>13.51</v>
+        <v>7.27</v>
       </c>
       <c r="M2" s="30" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>75 (A+)</t>
+          <t>72 (A+)</t>
         </is>
       </c>
       <c r="C3" s="30" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D3" s="30" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="E3" s="30" t="n">
-        <v>3.43</v>
+        <v>3.51</v>
       </c>
       <c r="F3" s="30" t="n">
-        <v>1.67</v>
+        <v>0.9</v>
       </c>
       <c r="G3" s="30" t="n">
-        <v>4.48</v>
+        <v>2.64</v>
       </c>
       <c r="H3" s="30" t="n"/>
       <c r="I3" s="30" t="n">
-        <v>2.07</v>
+        <v>0.68</v>
       </c>
       <c r="J3" s="30" t="n">
-        <v>4.15</v>
+        <v>18.86</v>
       </c>
       <c r="K3" s="30" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="L3" s="30" t="n">
-        <v>7.27</v>
+        <v>0</v>
       </c>
       <c r="M3" s="30" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>75 (A+)</t>
+          <t>72 (A+)</t>
         </is>
       </c>
       <c r="C4" s="30" t="n">
@@ -4245,17 +4245,17 @@
         <v>1.13</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>4.6</v>
+        <v>4.49</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>2.37</v>
+        <v>2.97</v>
       </c>
       <c r="G4" s="30" t="n">
         <v>4.32</v>
       </c>
       <c r="H4" s="30" t="n"/>
       <c r="I4" s="30" t="n">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="J4" s="30" t="n">
         <v>40.08</v>
@@ -4273,44 +4273,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>70 (A+)</t>
+          <t>71 (A+)</t>
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>2.77</v>
+        <v>-0.21</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>5.21</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>3.32</v>
+        <v>0.95</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="H5" s="30" t="n"/>
       <c r="I5" s="30" t="n">
-        <v>1.88</v>
+        <v>0.31</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>-7.56</v>
+        <v>24.76</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>6.47</v>
+        <v>8.35</v>
       </c>
       <c r="L5" s="30" t="n">
-        <v>-5.26</v>
+        <v>13.51</v>
       </c>
       <c r="M5" s="30" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>69 (A+)</t>
+          <t>70 (A+)</t>
         </is>
       </c>
       <c r="C6" s="30" t="n">
@@ -4331,17 +4331,17 @@
         <v>0.34</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="H6" s="30" t="n"/>
       <c r="I6" s="30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>-5.58</v>
@@ -4359,44 +4359,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>66 (A)</t>
+          <t>70 (A+)</t>
         </is>
       </c>
       <c r="C7" s="30" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="D7" s="30" t="n">
-        <v>0.54</v>
+        <v>2.77</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>2.84</v>
+        <v>5.3</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>1.04</v>
+        <v>3.12</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="30" t="n"/>
       <c r="I7" s="30" t="n">
-        <v>0.49</v>
+        <v>1.88</v>
       </c>
       <c r="J7" s="30" t="n">
-        <v>18.86</v>
+        <v>-7.56</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>7</v>
+        <v>6.47</v>
       </c>
       <c r="L7" s="30" t="n">
-        <v>0</v>
+        <v>-5.26</v>
       </c>
       <c r="M7" s="30" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C8" s="30" t="n">
@@ -4417,17 +4417,17 @@
         <v>-0.7</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="H8" s="30" t="n"/>
       <c r="I8" s="30" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>-23.67</v>
@@ -4445,93 +4445,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>63 (A-)</t>
+          <t>64 (A)</t>
         </is>
       </c>
       <c r="C9" s="30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="30" t="n">
-        <v>0.8</v>
+        <v>1.42</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>1.04</v>
+        <v>2.83</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>4.22</v>
+        <v>2.86</v>
       </c>
       <c r="H9" s="30" t="n"/>
       <c r="I9" s="30" t="n">
-        <v>1.7</v>
+        <v>0.83</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>-29.04</v>
+        <v>2.1</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>6.88</v>
+        <v>7.73</v>
       </c>
       <c r="L9" s="30" t="n">
-        <v>1.39</v>
+        <v>9.09</v>
       </c>
       <c r="M9" s="30" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>62 (A-)</t>
+          <t>63 (A-)</t>
         </is>
       </c>
       <c r="C10" s="30" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>1.42</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>1.51</v>
+        <v>5.08</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>2.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>2.52</v>
+        <v>4.4</v>
       </c>
       <c r="H10" s="30" t="n"/>
       <c r="I10" s="30" t="n">
-        <v>0.74</v>
+        <v>1.16</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>2.1</v>
+        <v>-29.04</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>7.73</v>
+        <v>6.88</v>
       </c>
       <c r="L10" s="30" t="n">
-        <v>9.09</v>
+        <v>1.39</v>
       </c>
       <c r="M10" s="30" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
@@ -4540,35 +4540,35 @@
         </is>
       </c>
       <c r="C11" s="30" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>1.61</v>
+        <v>0.98</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>4.48</v>
+        <v>4.21</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>1.7</v>
+        <v>3.86</v>
       </c>
       <c r="H11" s="30" t="n"/>
       <c r="I11" s="30" t="n">
-        <v>-0.02</v>
+        <v>1.46</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>25.84</v>
+        <v>-9.84</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>7.28</v>
+        <v>7.05</v>
       </c>
       <c r="L11" s="30" t="n">
-        <v>6</v>
+        <v>3.57</v>
       </c>
       <c r="M11" s="30" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>59 (B+)</t>
         </is>
       </c>
       <c r="C12" s="30" t="n">
@@ -4589,17 +4589,17 @@
         <v>0.79</v>
       </c>
       <c r="E12" s="30" t="n">
-        <v>3.44</v>
+        <v>4.03</v>
       </c>
       <c r="F12" s="30" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>4.18</v>
+        <v>4.4</v>
       </c>
       <c r="H12" s="30" t="n"/>
       <c r="I12" s="30" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>-13.44</v>
@@ -4617,222 +4617,222 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>58 (B+)</t>
         </is>
       </c>
       <c r="C13" s="30" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.98</v>
+        <v>1.61</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>3.95</v>
+        <v>3.33</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>2.68</v>
+        <v>1.95</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>3.86</v>
+        <v>1.68</v>
       </c>
       <c r="H13" s="30" t="n"/>
       <c r="I13" s="30" t="n">
-        <v>1.42</v>
+        <v>-0.05</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>-9.84</v>
+        <v>25.84</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>7.05</v>
+        <v>7.28</v>
       </c>
       <c r="L13" s="30" t="n">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="M13" s="30" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>57 (B+)</t>
         </is>
       </c>
       <c r="C14" s="30" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.95</v>
+        <v>0.22</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>4.66</v>
+        <v>6.12</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>3.86</v>
+        <v>3.96</v>
       </c>
       <c r="H14" s="30" t="n"/>
       <c r="I14" s="30" t="n">
-        <v>1.56</v>
+        <v>0.8</v>
       </c>
       <c r="J14" s="30" t="n">
-        <v>-21.89</v>
+        <v>-11.73</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>7</v>
+        <v>7.26</v>
       </c>
       <c r="L14" s="30" t="n">
-        <v>1.69</v>
+        <v>-2.6</v>
       </c>
       <c r="M14" s="30" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C15" s="30" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="D15" s="30" t="n">
-        <v>-0.92</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" s="30" t="n">
-        <v>6.63</v>
+        <v>5.99</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>0.38</v>
+        <v>2.14</v>
       </c>
       <c r="H15" s="30" t="n"/>
       <c r="I15" s="30" t="n">
-        <v>0.06</v>
+        <v>-0.47</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>5.95</v>
+        <v>-10.35</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>6.67</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L15" s="30" t="n">
-        <v>6.25</v>
+        <v>12.82</v>
       </c>
       <c r="M15" s="30" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C16" s="30" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>0.22</v>
+        <v>-0.48</v>
       </c>
       <c r="E16" s="30" t="n">
-        <v>5.78</v>
+        <v>-0.78</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>1.56</v>
+        <v>7.4</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>4.14</v>
+        <v>2.92</v>
       </c>
       <c r="H16" s="30" t="n"/>
       <c r="I16" s="30" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>-11.73</v>
+        <v>120.21</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>7.26</v>
+        <v>6</v>
       </c>
       <c r="L16" s="30" t="n">
-        <v>-2.6</v>
+        <v>-10</v>
       </c>
       <c r="M16" s="30" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>55 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C17" s="30" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>-0.48</v>
+        <v>-0.77</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>0.51</v>
+        <v>5.44</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>7.03</v>
+        <v>2.81</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="H17" s="30" t="n"/>
       <c r="I17" s="30" t="n">
-        <v>1.34</v>
+        <v>0.88</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>120.21</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="K17" s="30" t="n">
-        <v>6</v>
+        <v>7.23</v>
       </c>
       <c r="L17" s="30" t="n">
-        <v>-10</v>
+        <v>2.27</v>
       </c>
       <c r="M17" s="30" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
@@ -4841,35 +4841,35 @@
         </is>
       </c>
       <c r="C18" s="30" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>1.95</v>
+        <v>5.13</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>5.49</v>
+        <v>1.3</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="H18" s="30" t="n"/>
       <c r="I18" s="30" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>33.43</v>
+        <v>3.19</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>6.91</v>
+        <v>7.36</v>
       </c>
       <c r="L18" s="30" t="n">
-        <v>-3.45</v>
+        <v>-3.9</v>
       </c>
       <c r="M18" s="30" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -4890,17 +4890,17 @@
         <v>0.88</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="H19" s="30" t="n"/>
       <c r="I19" s="30" t="n">
-        <v>-0.11</v>
+        <v>-0.46</v>
       </c>
       <c r="J19" s="30" t="n">
         <v>7.37</v>
@@ -4918,7 +4918,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
@@ -4927,84 +4927,84 @@
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>-0.77</v>
+        <v>-1.35</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>5.79</v>
+        <v>4.15</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>2.82</v>
+        <v>1.63</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>3.2</v>
+        <v>0.82</v>
       </c>
       <c r="H20" s="30" t="n"/>
       <c r="I20" s="30" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J20" s="30" t="n">
-        <v>93.95999999999999</v>
+        <v>-37.46</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>7.23</v>
+        <v>7.73</v>
       </c>
       <c r="L20" s="30" t="n">
-        <v>2.27</v>
+        <v>7.32</v>
       </c>
       <c r="M20" s="30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>-0.5</v>
+        <v>-0.95</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>5.33</v>
+        <v>3.92</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>1.23</v>
+        <v>2.39</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="H21" s="30" t="n"/>
       <c r="I21" s="30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>3.19</v>
+        <v>-21.89</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>7.36</v>
+        <v>7</v>
       </c>
       <c r="L21" s="30" t="n">
-        <v>-3.9</v>
+        <v>1.69</v>
       </c>
       <c r="M21" s="30" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
@@ -5013,84 +5013,84 @@
         </is>
       </c>
       <c r="C22" s="30" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>-0.04</v>
+        <v>-0.22</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>4.94</v>
+        <v>7.68</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>1.16</v>
+        <v>3.13</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="H22" s="30" t="n"/>
       <c r="I22" s="30" t="n">
-        <v>-0.1</v>
+        <v>0.35</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>-10.35</v>
+        <v>-36.23</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>8.279999999999999</v>
+        <v>7.16</v>
       </c>
       <c r="L22" s="30" t="n">
-        <v>12.82</v>
+        <v>-5.56</v>
       </c>
       <c r="M22" s="30" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C23" s="30" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="D23" s="30" t="n">
-        <v>-1.35</v>
+        <v>-1.71</v>
       </c>
       <c r="E23" s="30" t="n">
-        <v>3.31</v>
+        <v>5.78</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="H23" s="30" t="n"/>
       <c r="I23" s="30" t="n">
-        <v>0.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J23" s="30" t="n">
-        <v>-37.46</v>
+        <v>32.14</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>7.73</v>
+        <v>5.44</v>
       </c>
       <c r="L23" s="30" t="n">
-        <v>7.32</v>
+        <v>-15.56</v>
       </c>
       <c r="M23" s="30" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
@@ -5099,41 +5099,41 @@
         </is>
       </c>
       <c r="C24" s="30" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="D24" s="30" t="n">
-        <v>0.28</v>
+        <v>-2.18</v>
       </c>
       <c r="E24" s="30" t="n">
-        <v>1.71</v>
+        <v>3.39</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>0.99</v>
+        <v>5.93</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>3.34</v>
+        <v>2.32</v>
       </c>
       <c r="H24" s="30" t="n"/>
       <c r="I24" s="30" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="J24" s="30" t="n">
-        <v>-6.61</v>
+        <v>17.69</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="L24" s="30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M24" s="30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
@@ -5142,41 +5142,39 @@
         </is>
       </c>
       <c r="C25" s="30" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>-0.22</v>
+        <v>1.8</v>
       </c>
       <c r="E25" s="30" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="F25" s="30" t="n">
-        <v>3.22</v>
-      </c>
+        <v>0.88</v>
+      </c>
+      <c r="F25" s="30" t="n"/>
       <c r="G25" s="30" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="H25" s="30" t="n"/>
       <c r="I25" s="30" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>-36.23</v>
+        <v>-16.61</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>7.16</v>
+        <v>7.26</v>
       </c>
       <c r="L25" s="30" t="n">
-        <v>-5.56</v>
+        <v>7.84</v>
       </c>
       <c r="M25" s="30" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
@@ -5185,211 +5183,213 @@
         </is>
       </c>
       <c r="C26" s="30" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>-2.2</v>
+        <v>0.28</v>
       </c>
       <c r="E26" s="30" t="n">
-        <v>5.31</v>
+        <v>1.21</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>1.98</v>
+        <v>3.62</v>
       </c>
       <c r="H26" s="30" t="n"/>
       <c r="I26" s="30" t="n">
-        <v>-2.15</v>
+        <v>1.3</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>40.37</v>
+        <v>-6.61</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>8.029999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="L26" s="30" t="n">
-        <v>10.26</v>
+        <v>1.96</v>
       </c>
       <c r="M26" s="30" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="30" t="n">
-        <v>-2.18</v>
+        <v>-2.2</v>
       </c>
       <c r="E27" s="30" t="n">
-        <v>3.48</v>
+        <v>5.85</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>5.84</v>
+        <v>1.58</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="H27" s="30" t="n"/>
       <c r="I27" s="30" t="n">
-        <v>1.83</v>
+        <v>-1.96</v>
       </c>
       <c r="J27" s="30" t="n">
-        <v>17.69</v>
+        <v>40.37</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>7</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L27" s="30" t="n">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="M27" s="30" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C28" s="30" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="D28" s="30" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="E28" s="30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F28" s="30" t="n"/>
+        <v>1.91</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <v>5.05</v>
+      </c>
       <c r="G28" s="30" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H28" s="30" t="n"/>
       <c r="I28" s="30" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>-16.61</v>
+        <v>33.43</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>7.26</v>
+        <v>6.91</v>
       </c>
       <c r="L28" s="30" t="n">
-        <v>7.84</v>
+        <v>-3.45</v>
       </c>
       <c r="M28" s="30" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="D29" s="30" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E29" s="30" t="n">
-        <v>4.86</v>
+        <v>3.73</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>1.74</v>
+        <v>0.95</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>0.6</v>
+        <v>3.22</v>
       </c>
       <c r="H29" s="30" t="n"/>
       <c r="I29" s="30" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="J29" s="30" t="n">
-        <v>17.78</v>
+        <v>19.22</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="L29" s="30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" s="30" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="D30" s="30" t="n">
-        <v>-1.71</v>
+        <v>2.87</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>5.99</v>
+        <v>2.93</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>4.09</v>
+        <v>3.56</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="H30" s="30" t="n"/>
       <c r="I30" s="30" t="n">
-        <v>0.22</v>
+        <v>-0.12</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>32.14</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>5.44</v>
+        <v>7.8</v>
       </c>
       <c r="L30" s="30" t="n">
-        <v>-15.56</v>
+        <v>13.33</v>
       </c>
       <c r="M30" s="30" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
@@ -5398,170 +5398,170 @@
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D31" s="30" t="n">
-        <v>-1.1</v>
+        <v>-1.67</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>0.57</v>
+        <v>2.15</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>2.63</v>
+        <v>1.79</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="H31" s="30" t="n"/>
       <c r="I31" s="30" t="n">
-        <v>0.65</v>
+        <v>0.1</v>
       </c>
       <c r="J31" s="30" t="n">
-        <v>39.5</v>
+        <v>-17.89</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>7.01</v>
+        <v>6.97</v>
       </c>
       <c r="L31" s="30" t="n">
-        <v>1.72</v>
+        <v>-1.72</v>
       </c>
       <c r="M31" s="30" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="D32" s="30" t="n">
-        <v>2.87</v>
+        <v>-0.5</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>3.84</v>
+        <v>1.67</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>2.84</v>
+        <v>0.8</v>
       </c>
       <c r="H32" s="30" t="n"/>
       <c r="I32" s="30" t="n">
-        <v>0.27</v>
+        <v>0.74</v>
       </c>
       <c r="J32" s="30" t="n">
-        <v>87.23999999999999</v>
+        <v>17.78</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>7.8</v>
+        <v>7.33</v>
       </c>
       <c r="L32" s="30" t="n">
-        <v>13.33</v>
+        <v>10</v>
       </c>
       <c r="M32" s="30" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="D33" s="30" t="n">
-        <v>-1.67</v>
+        <v>-1.1</v>
       </c>
       <c r="E33" s="30" t="n">
-        <v>1.94</v>
+        <v>0.03</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>1.86</v>
+        <v>3.04</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="H33" s="30" t="n"/>
       <c r="I33" s="30" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="J33" s="30" t="n">
-        <v>-17.89</v>
+        <v>39.5</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>6.97</v>
+        <v>7.01</v>
       </c>
       <c r="L33" s="30" t="n">
-        <v>-1.72</v>
+        <v>1.72</v>
       </c>
       <c r="M33" s="30" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>44 (B-)</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="D34" s="30" t="n">
-        <v>1.69</v>
+        <v>-0.91</v>
       </c>
       <c r="E34" s="30" t="n">
-        <v>2.76</v>
+        <v>5.51</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>7.48</v>
+        <v>2.47</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="H34" s="30" t="n"/>
       <c r="I34" s="30" t="n">
-        <v>0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>5.95</v>
+        <v>77.17</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>7.26</v>
+        <v>6.76</v>
       </c>
       <c r="L34" s="30" t="n">
-        <v>2.63</v>
+        <v>-2.44</v>
       </c>
       <c r="M34" s="30" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B35" s="31" t="inlineStr">
@@ -5570,41 +5570,41 @@
         </is>
       </c>
       <c r="C35" s="30" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="D35" s="30" t="n">
-        <v>-1.42</v>
+        <v>1.69</v>
       </c>
       <c r="E35" s="30" t="n">
-        <v>5.14</v>
+        <v>3.09</v>
       </c>
       <c r="F35" s="30" t="n">
-        <v>3.03</v>
+        <v>7.47</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="H35" s="30" t="n"/>
       <c r="I35" s="30" t="n">
-        <v>2.47</v>
+        <v>0.6</v>
       </c>
       <c r="J35" s="30" t="n">
-        <v>-6.89</v>
+        <v>5.95</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>7</v>
+        <v>7.26</v>
       </c>
       <c r="L35" s="30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M35" s="30" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B36" s="31" t="inlineStr">
@@ -5613,112 +5613,112 @@
         </is>
       </c>
       <c r="C36" s="30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D36" s="30" t="n">
-        <v>-2.7</v>
+        <v>-1.75</v>
       </c>
       <c r="E36" s="30" t="n">
-        <v>2.61</v>
+        <v>7.5</v>
       </c>
       <c r="F36" s="30" t="n">
-        <v>2.45</v>
+        <v>4.31</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>3.52</v>
+        <v>2.58</v>
       </c>
       <c r="H36" s="30" t="n"/>
       <c r="I36" s="30" t="n">
-        <v>1.23</v>
+        <v>0.7</v>
       </c>
       <c r="J36" s="30" t="n">
-        <v>-18.76</v>
+        <v>-37.09</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L36" s="30" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
       <c r="M36" s="30" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="D37" s="30" t="n">
-        <v>-0.91</v>
+        <v>-2.7</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>5.54</v>
+        <v>3.28</v>
       </c>
       <c r="F37" s="30" t="n">
-        <v>2.96</v>
+        <v>2.11</v>
       </c>
       <c r="G37" s="30" t="n">
-        <v>1.82</v>
+        <v>3.36</v>
       </c>
       <c r="H37" s="30" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>-0.68</v>
+        <v>0.91</v>
       </c>
       <c r="J37" s="30" t="n">
-        <v>77.17</v>
+        <v>-18.76</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>6.76</v>
+        <v>7.2</v>
       </c>
       <c r="L37" s="30" t="n">
-        <v>-2.44</v>
+        <v>-4.29</v>
       </c>
       <c r="M37" s="30" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="D38" s="30" t="n">
-        <v>0.1</v>
+        <v>-1.32</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>2.2</v>
+        <v>0.27</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>3.22</v>
+        <v>2.28</v>
       </c>
       <c r="H38" s="30" t="n"/>
       <c r="I38" s="30" t="n">
-        <v>0.85</v>
+        <v>1.39</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>19.22</v>
+        <v>31.92</v>
       </c>
       <c r="K38" s="30" t="n">
         <v>7</v>
@@ -5727,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="30" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
@@ -5748,17 +5748,17 @@
         <v>-0.58</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>5.27</v>
+        <v>5.68</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="H39" s="30" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>-1.44</v>
+        <v>-1.52</v>
       </c>
       <c r="J39" s="30" t="n">
         <v>12.62</v>
@@ -5776,93 +5776,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="D40" s="30" t="n">
-        <v>0.85</v>
+        <v>-0.92</v>
       </c>
       <c r="E40" s="30" t="n">
-        <v>1.46</v>
+        <v>4.52</v>
       </c>
       <c r="F40" s="30" t="n">
-        <v>4.25</v>
+        <v>0.86</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>1.94</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="30" t="n"/>
       <c r="I40" s="30" t="n">
-        <v>-0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>-10.38</v>
+        <v>5.95</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>8.25</v>
+        <v>6.67</v>
       </c>
       <c r="L40" s="30" t="n">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="M40" s="30" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>37 (C)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="D41" s="30" t="n">
-        <v>-1.75</v>
+        <v>-1.92</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>6.72</v>
+        <v>2.02</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>4.58</v>
+        <v>3.35</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>2.92</v>
+        <v>0.78</v>
       </c>
       <c r="H41" s="30" t="n"/>
       <c r="I41" s="30" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>-37.09</v>
+        <v>21.94</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>7</v>
+        <v>6.87</v>
       </c>
       <c r="L41" s="30" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="M41" s="30" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B42" s="31" t="inlineStr">
@@ -5871,41 +5871,41 @@
         </is>
       </c>
       <c r="C42" s="30" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="D42" s="30" t="n">
-        <v>-1.75</v>
+        <v>0.85</v>
       </c>
       <c r="E42" s="30" t="n">
-        <v>6.02</v>
+        <v>0.52</v>
       </c>
       <c r="F42" s="30" t="n">
-        <v>2.96</v>
+        <v>5.18</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>0.16</v>
+        <v>2.06</v>
       </c>
       <c r="H42" s="30" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>0.79</v>
+        <v>-0.25</v>
       </c>
       <c r="J42" s="30" t="n">
-        <v>-13.3</v>
+        <v>-10.38</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>7.09</v>
+        <v>8.25</v>
       </c>
       <c r="L42" s="30" t="n">
-        <v>-4.55</v>
+        <v>12.5</v>
       </c>
       <c r="M42" s="30" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B43" s="31" t="inlineStr">
@@ -5914,35 +5914,35 @@
         </is>
       </c>
       <c r="C43" s="30" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="D43" s="30" t="n">
-        <v>-1.32</v>
+        <v>-1.75</v>
       </c>
       <c r="E43" s="30" t="n">
-        <v>-0.14</v>
+        <v>5.51</v>
       </c>
       <c r="F43" s="30" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>1.8</v>
+        <v>0.16</v>
       </c>
       <c r="H43" s="30" t="n"/>
       <c r="I43" s="30" t="n">
-        <v>1.36</v>
+        <v>0.75</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>31.92</v>
+        <v>-13.3</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="L43" s="30" t="n">
-        <v>0</v>
+        <v>-4.55</v>
       </c>
       <c r="M43" s="30" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>32 (C-)</t>
+          <t>34 (C)</t>
         </is>
       </c>
       <c r="C44" s="30" t="n">
@@ -5963,17 +5963,17 @@
         <v>-0.99</v>
       </c>
       <c r="E44" s="30" t="n">
-        <v>0.09</v>
+        <v>0.58</v>
       </c>
       <c r="F44" s="30" t="n">
-        <v>4.62</v>
+        <v>4.49</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="H44" s="30" t="n"/>
       <c r="I44" s="30" t="n">
-        <v>-1.17</v>
+        <v>-1.05</v>
       </c>
       <c r="J44" s="30" t="n">
         <v>-3.15</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B45" s="31" t="inlineStr">
         <is>
-          <t>32 (C-)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C45" s="30" t="n">
@@ -6006,17 +6006,17 @@
         <v>-7.49</v>
       </c>
       <c r="E45" s="30" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="F45" s="30" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="H45" s="30" t="n"/>
       <c r="I45" s="30" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="J45" s="30" t="n">
         <v>-3.73</v>
@@ -6034,136 +6034,136 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>31 (C-)</t>
+          <t>32 (C)</t>
         </is>
       </c>
       <c r="C46" s="30" t="n">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="D46" s="30" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.42</v>
       </c>
       <c r="E46" s="30" t="n">
-        <v>2.49</v>
+        <v>4.51</v>
       </c>
       <c r="F46" s="30" t="n">
-        <v>3.51</v>
+        <v>2.73</v>
       </c>
       <c r="G46" s="30" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="H46" s="30" t="n"/>
       <c r="I46" s="30" t="n">
-        <v>-0.76</v>
+        <v>0.79</v>
       </c>
       <c r="J46" s="30" t="n">
-        <v>10.33</v>
+        <v>-6.89</v>
       </c>
       <c r="K46" s="30" t="n">
-        <v>6.56</v>
+        <v>7</v>
       </c>
       <c r="L46" s="30" t="n">
-        <v>-4.35</v>
+        <v>0</v>
       </c>
       <c r="M46" s="30" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>29 (C-)</t>
+          <t>30 (C-)</t>
         </is>
       </c>
       <c r="C47" s="30" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="D47" s="30" t="n">
-        <v>-0.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E47" s="30" t="n">
-        <v>0.39</v>
+        <v>2.4</v>
       </c>
       <c r="F47" s="30" t="n">
-        <v>1.75</v>
+        <v>3.54</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>2.74</v>
+        <v>1.74</v>
       </c>
       <c r="H47" s="30" t="n"/>
       <c r="I47" s="30" t="n">
-        <v>0.36</v>
+        <v>-0.82</v>
       </c>
       <c r="J47" s="30" t="n">
-        <v>-10.28</v>
+        <v>10.33</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>7.41</v>
+        <v>6.56</v>
       </c>
       <c r="L47" s="30" t="n">
-        <v>-12.16</v>
+        <v>-4.35</v>
       </c>
       <c r="M47" s="30" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>28 (C-)</t>
+          <t>29 (C-)</t>
         </is>
       </c>
       <c r="C48" s="30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>-1.92</v>
+        <v>-0.29</v>
       </c>
       <c r="E48" s="30" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="F48" s="30" t="n">
-        <v>4.13</v>
+        <v>2.07</v>
       </c>
       <c r="G48" s="30" t="n">
-        <v>0.72</v>
+        <v>2.8</v>
       </c>
       <c r="H48" s="30" t="n"/>
       <c r="I48" s="30" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="J48" s="30" t="n">
-        <v>21.94</v>
+        <v>-10.28</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>6.87</v>
+        <v>7.41</v>
       </c>
       <c r="L48" s="30" t="n">
-        <v>-1.96</v>
+        <v>-12.16</v>
       </c>
       <c r="M48" s="30" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B49" s="31" t="inlineStr">
@@ -6172,41 +6172,41 @@
         </is>
       </c>
       <c r="C49" s="30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D49" s="30" t="n">
-        <v>0.25</v>
+        <v>-2.46</v>
       </c>
       <c r="E49" s="30" t="n">
-        <v>1.61</v>
+        <v>3.28</v>
       </c>
       <c r="F49" s="30" t="n">
-        <v>2.89</v>
+        <v>3.65</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>0.38</v>
+        <v>2.54</v>
       </c>
       <c r="H49" s="30" t="n"/>
       <c r="I49" s="30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="J49" s="30" t="n">
-        <v>-31.66</v>
+        <v>-42.35</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>8.279999999999999</v>
+        <v>6.73</v>
       </c>
       <c r="L49" s="30" t="n">
-        <v>12.82</v>
+        <v>-2.7</v>
       </c>
       <c r="M49" s="30" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B50" s="31" t="inlineStr">
@@ -6215,41 +6215,41 @@
         </is>
       </c>
       <c r="C50" s="30" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="D50" s="30" t="n">
-        <v>-2.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E50" s="30" t="n">
-        <v>3.11</v>
+        <v>1.48</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>3.69</v>
+        <v>2.57</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H50" s="30" t="n"/>
       <c r="I50" s="30" t="n">
-        <v>0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>-42.35</v>
+        <v>-18.71</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>6.73</v>
+        <v>7.53</v>
       </c>
       <c r="L50" s="30" t="n">
-        <v>-2.7</v>
+        <v>5.26</v>
       </c>
       <c r="M50" s="30" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B51" s="31" t="inlineStr">
@@ -6258,35 +6258,35 @@
         </is>
       </c>
       <c r="C51" s="30" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="D51" s="30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="E51" s="30" t="n">
-        <v>0.6</v>
+        <v>1.74</v>
       </c>
       <c r="F51" s="30" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="G51" s="30" t="n">
-        <v>2.22</v>
+        <v>0.32</v>
       </c>
       <c r="H51" s="30" t="n"/>
       <c r="I51" s="30" t="n">
-        <v>0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="J51" s="30" t="n">
-        <v>-18.71</v>
+        <v>-31.66</v>
       </c>
       <c r="K51" s="30" t="n">
-        <v>7.53</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L51" s="30" t="n">
-        <v>5.26</v>
+        <v>12.82</v>
       </c>
       <c r="M51" s="30" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -6368,41 +6368,41 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="G2" s="11" t="n">
+      <c r="D2" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G2" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H2" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="I2" s="11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J2" s="11" t="n">
-        <v>5.49</v>
+      <c r="I2" s="14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>5.05</v>
       </c>
     </row>
     <row r="3">
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="D3" s="14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="F3" s="14" t="n">
-        <v>47.3</v>
+        <v>49.1</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>5</v>
@@ -6437,10 +6437,10 @@
         <v>-2.18</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="J3" s="14" t="n">
-        <v>5.84</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="4">
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="F4" s="23" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="G4" s="23" t="n">
         <v>4.9</v>
@@ -6475,48 +6475,48 @@
         <v>-2.46</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="J4" s="23" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="D5" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G5" s="8" t="n">
         <v>4.6</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="8" t="n">
         <v>0.79</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>1.01</v>
+      <c r="I5" s="8" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="6">
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>49.2</v>
+        <v>47.6</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>5.1</v>
@@ -6551,48 +6551,48 @@
         <v>0.28</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>1.71</v>
+        <v>1.21</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>0.99</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="D7" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>3.7</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="11" t="n">
         <v>-0.22</v>
       </c>
-      <c r="I7" s="14" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>3.22</v>
+      <c r="I7" s="11" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>3.13</v>
       </c>
     </row>
     <row r="8">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>4</v>
@@ -6627,10 +6627,10 @@
         <v>-2.2</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>5.31</v>
+        <v>5.85</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>3.2</v>
@@ -6665,48 +6665,48 @@
         <v>0.88</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="G10" s="5" t="n">
+      <c r="D10" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="2" t="n">
         <v>1.42</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>2.65</v>
+      <c r="I10" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="11">
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>42.1</v>
+        <v>41.4</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>4.8</v>
@@ -6741,48 +6741,48 @@
         <v>-2.7</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>2.61</v>
+        <v>3.28</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="G12" s="17" t="n">
+      <c r="D12" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G12" s="14" t="n">
         <v>3.9</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="14" t="n">
         <v>2.87</v>
       </c>
-      <c r="I12" s="17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>3.84</v>
+      <c r="I12" s="14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>3.56</v>
       </c>
     </row>
     <row r="13">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>5.7</v>
@@ -6817,48 +6817,48 @@
         <v>-1.75</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>6.02</v>
+        <v>5.51</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
-        <v>46</v>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="G14" s="14" t="n">
+      <c r="D14" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="G14" s="11" t="n">
         <v>4.4</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="11" t="n">
         <v>-1.71</v>
       </c>
-      <c r="I14" s="14" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>4.09</v>
+      <c r="I14" s="11" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>27.4</v>
+        <v>26.9</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>6</v>
@@ -6893,10 +6893,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>0.6</v>
+        <v>1.48</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="16">
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>5</v>
@@ -6931,48 +6931,48 @@
         <v>-0.77</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>5.79</v>
+        <v>5.44</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D17" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="G17" s="20" t="n">
+      <c r="D17" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G17" s="17" t="n">
         <v>4.4</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="17" t="n">
         <v>-1.32</v>
       </c>
-      <c r="I17" s="20" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <v>2.72</v>
+      <c r="I17" s="17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="18">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>51.2</v>
+        <v>52.5</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>4.8</v>
@@ -7007,86 +7007,86 @@
         <v>-0.5</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>5.33</v>
+        <v>5.13</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="G19" s="20" t="n">
+      <c r="D19" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="G19" s="17" t="n">
         <v>4.7</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="17" t="n">
         <v>-1.75</v>
       </c>
-      <c r="I19" s="20" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="J19" s="20" t="n">
-        <v>4.58</v>
+      <c r="I19" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>4.31</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n">
+      <c r="A20" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G20" s="17" t="n">
+      <c r="D20" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G20" s="14" t="n">
         <v>4.1</v>
       </c>
-      <c r="H20" s="17" t="n">
+      <c r="H20" s="14" t="n">
         <v>-1.67</v>
       </c>
-      <c r="I20" s="17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J20" s="17" t="n">
-        <v>1.86</v>
+      <c r="I20" s="14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="21">
@@ -7121,7 +7121,7 @@
         <v>0.22</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>5.78</v>
+        <v>6.12</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>1.56</v>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>63.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3.7</v>
@@ -7159,10 +7159,10 @@
         <v>-0.7</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="23">
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>51.3</v>
+        <v>54</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>4.2</v>
@@ -7197,10 +7197,10 @@
         <v>-0.04</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>4.94</v>
+        <v>5.99</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="24">
@@ -7218,15 +7218,15 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>66</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>3.8</v>
@@ -7235,48 +7235,48 @@
         <v>0.54</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2.84</v>
+        <v>3.51</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.04</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n">
+      <c r="A25" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="G25" s="17" t="n">
+      <c r="D25" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G25" s="14" t="n">
         <v>4.7</v>
       </c>
-      <c r="H25" s="17" t="n">
+      <c r="H25" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="I25" s="17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J25" s="17" t="n">
-        <v>1.12</v>
+      <c r="I25" s="14" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="26">
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>4</v>
@@ -7311,10 +7311,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>4.8</v>
+        <v>5.08</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1.04</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>39.4</v>
+        <v>39.8</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>4.9</v>
@@ -7349,86 +7349,86 @@
         <v>-0.58</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>5.27</v>
+        <v>5.68</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="n">
+      <c r="A28" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>Sacramento</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="G28" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="23" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="I28" s="23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J28" s="23" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="G29" s="5" t="n">
+      <c r="D29" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G29" s="8" t="n">
         <v>3.7</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="8" t="n">
         <v>1.61</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>2.06</v>
+      <c r="I29" s="8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="30">
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>59.6</v>
+        <v>61</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>5.4</v>
@@ -7463,10 +7463,10 @@
         <v>0.98</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>3.95</v>
+        <v>4.21</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="31">
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>3.7</v>
@@ -7501,10 +7501,10 @@
         <v>-0.21</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7.22</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="32">
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>69.3</v>
+        <v>69.7</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.8</v>
@@ -7539,10 +7539,10 @@
         <v>0.34</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="33">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>50.3</v>
+        <v>51.7</v>
       </c>
       <c r="G33" s="11" t="n">
         <v>3.2</v>
@@ -7577,48 +7577,48 @@
         <v>-1.35</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>3.31</v>
+        <v>4.15</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="n">
+      <c r="A34" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D34" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="G34" s="23" t="n">
+      <c r="D34" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G34" s="20" t="n">
         <v>3.4</v>
       </c>
-      <c r="H34" s="23" t="n">
+      <c r="H34" s="20" t="n">
         <v>-0.99</v>
       </c>
-      <c r="I34" s="23" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J34" s="23" t="n">
-        <v>4.62</v>
+      <c r="I34" s="20" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J34" s="20" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="35">
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>47.1</v>
+        <v>49.4</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>3.4</v>
@@ -7653,46 +7653,46 @@
         <v>1.8</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0.1</v>
+        <v>0.88</v>
       </c>
       <c r="J35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="G36" s="5" t="n">
+      <c r="D36" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G36" s="11" t="n">
         <v>3.1</v>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" s="11" t="n">
         <v>-0.95</v>
       </c>
-      <c r="I36" s="5" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>2.46</v>
+      <c r="I36" s="11" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>2.39</v>
       </c>
     </row>
     <row r="37">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>54.7</v>
+        <v>54.4</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>4.1</v>
@@ -7727,48 +7727,48 @@
         <v>-0.48</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0.51</v>
+        <v>-0.78</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>7.03</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G38" s="17" t="n">
+      <c r="D38" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G38" s="14" t="n">
         <v>3.9</v>
       </c>
-      <c r="H38" s="17" t="n">
+      <c r="H38" s="14" t="n">
         <v>-0.91</v>
       </c>
-      <c r="I38" s="17" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="J38" s="17" t="n">
-        <v>2.96</v>
+      <c r="I38" s="14" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>2.47</v>
       </c>
     </row>
     <row r="39">
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="F39" s="23" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="G39" s="23" t="n">
         <v>4.9</v>
@@ -7803,10 +7803,10 @@
         <v>-0.29</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>0.39</v>
+        <v>1.34</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="40">
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="D40" s="17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>44</v>
+        <v>43.1</v>
       </c>
       <c r="G40" s="17" t="n">
         <v>4.3</v>
@@ -7841,48 +7841,48 @@
         <v>1.69</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>2.76</v>
+        <v>3.09</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>7.48</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="n">
+      <c r="A41" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>Milwaukee-Waukesha</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="D41" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="G41" s="17" t="n">
+      <c r="D41" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="G41" s="20" t="n">
         <v>3.8</v>
       </c>
-      <c r="H41" s="17" t="n">
+      <c r="H41" s="20" t="n">
         <v>0.85</v>
       </c>
-      <c r="I41" s="17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="J41" s="17" t="n">
-        <v>4.25</v>
+      <c r="I41" s="20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J41" s="20" t="n">
+        <v>5.18</v>
       </c>
     </row>
     <row r="42">
@@ -7900,7 +7900,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3.2</v>
@@ -7917,10 +7917,10 @@
         <v>0.48</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3.43</v>
+        <v>3.16</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="43">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>47.4</v>
+        <v>45</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>4.3</v>
@@ -7955,10 +7955,10 @@
         <v>-0.5</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>4.86</v>
+        <v>4.2</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="44">
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="D44" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         </is>
       </c>
       <c r="F44" s="23" t="n">
-        <v>27.8</v>
+        <v>27</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>4.8</v>
@@ -7993,10 +7993,10 @@
         <v>0.25</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>2.89</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="45">
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="D45" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="F45" s="23" t="n">
-        <v>30.9</v>
+        <v>30.4</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>3.8</v>
@@ -8031,48 +8031,48 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="G46" s="5" t="n">
+      <c r="D46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G46" s="17" t="n">
         <v>4.7</v>
       </c>
-      <c r="H46" s="5" t="n">
+      <c r="H46" s="17" t="n">
         <v>-0.92</v>
       </c>
-      <c r="I46" s="5" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>0.89</v>
+      <c r="I46" s="17" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="47">
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.5</v>
@@ -8107,10 +8107,10 @@
         <v>1.13</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>4.6</v>
+        <v>4.49</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.37</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="48">
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>3.5</v>
@@ -8145,86 +8145,86 @@
         <v>-1.1</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>0.57</v>
+        <v>0.03</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="n">
+      <c r="A49" s="20" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="D49" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G49" s="17" t="n">
+      <c r="D49" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G49" s="20" t="n">
         <v>7.7</v>
       </c>
-      <c r="H49" s="17" t="n">
+      <c r="H49" s="20" t="n">
         <v>-1.42</v>
       </c>
-      <c r="I49" s="17" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="J49" s="17" t="n">
-        <v>3.03</v>
+      <c r="I49" s="20" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="J49" s="20" t="n">
+        <v>2.73</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="n">
+      <c r="A50" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids</t>
         </is>
       </c>
-      <c r="D50" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="G50" s="23" t="n">
+      <c r="D50" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G50" s="20" t="n">
         <v>4.3</v>
       </c>
-      <c r="H50" s="23" t="n">
+      <c r="H50" s="20" t="n">
         <v>-7.49</v>
       </c>
-      <c r="I50" s="23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="J50" s="23" t="n">
-        <v>4.66</v>
+      <c r="I50" s="20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J50" s="20" t="n">
+        <v>4.59</v>
       </c>
     </row>
     <row r="51">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8259,10 +8259,10 @@
         <v>2.77</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5.21</v>
+        <v>5.3</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>
@@ -8349,11 +8349,11 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="C3" s="36" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="36" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="G3" s="37" t="n">
@@ -8383,11 +8383,11 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C4" s="36" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="G4" s="37" t="n">
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="C5" s="36" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
@@ -8437,11 +8437,11 @@
         </is>
       </c>
       <c r="G5" s="37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8451,11 +8451,11 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
@@ -8471,11 +8471,11 @@
         </is>
       </c>
       <c r="G6" s="37" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
@@ -8501,15 +8501,15 @@
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="G7" s="37" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8519,15 +8519,15 @@
       </c>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E8" s="37" t="n">
@@ -8535,11 +8535,11 @@
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G8" s="37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="37" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
@@ -8569,11 +8569,11 @@
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="G9" s="37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9" s="37" t="inlineStr">
         <is>
@@ -8587,15 +8587,15 @@
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E10" s="37" t="n">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="G10" s="37" t="n">
@@ -8621,11 +8621,11 @@
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G11" s="37" t="n">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="F12" s="37" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="G12" s="37" t="n">

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -64,12 +64,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D1E7DD"/>
         <bgColor rgb="00D1E7DD"/>
       </patternFill>
@@ -102,6 +96,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
         <bgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B084"/>
+        <bgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
     <fill>
@@ -212,10 +212,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>73.8</v>
+        <v>72</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -685,16 +685,16 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -716,20 +716,20 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>72.2</v>
+        <v>71.2</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -747,20 +747,20 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -778,20 +778,20 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>69.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -822,19 +822,19 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>70.5</v>
+        <v>67.7</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -871,1146 +871,1146 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Austin-Round Rock-San Marcos</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D11" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Very Good</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Las Vegas</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="D12" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="F12" s="5" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="F13" s="5" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="F14" s="5" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Above Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="F16" s="8" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>San Francisco-Oakland-Fremont</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta-Sandy Springs-Roswell</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Seattle-Tacoma-Bellevue</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Los Angeles-Long Beach-Anaheim</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Tampa-St. Petersburg-Clearwater</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Houston-Pasadena-The Woodlands</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Washington-Arlington-Alexandria</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>San Antonio-New Braunfels</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>New York Newark-Jersey City</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Phoenix-Mesa-Chandler</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Boston-Cambridge-Newton</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Denver-Aurora-Centennial</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>San Jose</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
-        <v>54</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Seattle-Tacoma-Bellevue</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>53</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>53</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Nashville</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>51</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco-Oakland-Fremont</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>51</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="D33" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="F33" s="11" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Below Average</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="n">
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Providence-Warwick</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>San Diego-Chula Vista-Carlsbad</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Portland-Vancouver-Hillsboro</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Minneapolis-St. Paul-Bloomington</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Milwaukee-Waukesha</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Virginia Beach</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Riverside-San Bernardino-Ontario</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Houston-Pasadena-The Woodlands</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Washington-Arlington-Alexandria</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Washington DC</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>New York Newark-Jersey City</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>San Antonio-New Braunfels</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Boston-Cambridge-Newton</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Denver-Aurora-Centennial</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="n">
-        <v>42</v>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="n">
-        <v>37</v>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="n">
         <v>44</v>
       </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>Providence-Warwick</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>Phoenix-Mesa-Chandler</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>41</v>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>Portland-Vancouver-Hillsboro</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="n">
-        <v>27</v>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>Sacramento-Roseville-Folsom</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>39</v>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t>Milwaukee-Waukesha</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="n">
-        <v>36</v>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F42" s="20" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="G42" s="21" t="inlineStr">
+      <c r="F44" s="17" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>Very Poor</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B43" s="21" t="inlineStr">
-        <is>
-          <t>Riverside-San Bernardino-Ontario</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Indianapolis-Carmel-Greenwood</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F43" s="20" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="G43" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="B44" s="21" t="inlineStr">
-        <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G44" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>Grand Rapids</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
+      <c r="F45" s="17" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
         <is>
           <t>Very Poor</t>
         </is>
@@ -2035,137 +2035,137 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Grand Rapids</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F46" s="20" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="G46" s="21" t="inlineStr">
+      <c r="F47" s="17" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
         <is>
           <t>Very Poor</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>Chicago-Naperville-Elgin</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E49" s="21" t="inlineStr">
         <is>
           <t>C-</t>
         </is>
       </c>
-      <c r="F47" s="23" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="G47" s="24" t="inlineStr">
+      <c r="F49" s="20" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="23" t="n">
-        <v>38</v>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>Jacksonville</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>Jacksonville</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>Louisville-Jefferson County</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
         <is>
           <t>C-</t>
         </is>
       </c>
-      <c r="F48" s="23" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>Chicago-Naperville-Elgin</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="n">
-        <v>28</v>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Detroit-Warren-Dearborn</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="n">
+      <c r="F50" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
+      <c r="G50" s="21" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2173,32 +2173,32 @@
     </row>
     <row r="51">
       <c r="A51" s="23" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F51" s="23" t="n">
-        <v>27</v>
+        <v>25.7</v>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="B2" s="26" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" s="27" t="n">
         <v>84</v>
@@ -2323,8 +2323,8 @@
       <c r="I2" s="27" t="n">
         <v>98</v>
       </c>
-      <c r="J2" s="28" t="n">
-        <v>54</v>
+      <c r="J2" s="29" t="n">
+        <v>36</v>
       </c>
       <c r="K2" s="28" t="n">
         <v>52</v>
@@ -2333,141 +2333,141 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B3" s="26" t="n">
         <v>72</v>
       </c>
       <c r="C3" s="27" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D3" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="E3" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="F3" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="G3" s="28" t="n">
-        <v>54</v>
+        <v>86</v>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="F3" s="29" t="n">
+        <v>37</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>92</v>
       </c>
       <c r="H3" s="30" t="n"/>
       <c r="I3" s="27" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J3" s="27" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K3" s="29" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B4" s="26" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D4" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="E4" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="F4" s="29" t="n">
-        <v>37</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>92</v>
+        <v>70</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>96</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>54</v>
       </c>
       <c r="H4" s="30" t="n"/>
       <c r="I4" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="J4" s="27" t="n">
-        <v>88</v>
+        <v>78</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <v>66</v>
       </c>
       <c r="K4" s="29" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H5" s="30" t="n"/>
-      <c r="I5" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="J5" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="K5" s="27" t="n">
-        <v>98</v>
+      <c r="I5" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H6" s="30" t="n"/>
-      <c r="I6" s="27" t="n">
-        <v>70</v>
+      <c r="I6" s="29" t="n">
+        <v>32</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="K6" s="29" t="n">
-        <v>28</v>
+        <v>46</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>98</v>
@@ -2499,7 +2499,7 @@
         <v>86</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K7" s="29" t="n">
         <v>4</v>
@@ -2543,106 +2543,106 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>64</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>72</v>
+        <v>67</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>44</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>88</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>39</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>60</v>
+        <v>78</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>94</v>
       </c>
       <c r="H9" s="30" t="n"/>
       <c r="I9" s="27" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J9" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="K9" s="27" t="n">
-        <v>84</v>
+      <c r="K9" s="29" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B10" s="26" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>94</v>
+        <v>84</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>49</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H10" s="30" t="n"/>
       <c r="I10" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="29" t="n">
-        <v>16</v>
+        <v>92</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="K10" s="28" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B11" s="26" t="n">
-        <v>61</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>30</v>
+        <v>65</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>72</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="E11" s="28" t="n">
+        <v>88</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" s="28" t="n">
         <v>60</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>88</v>
       </c>
       <c r="H11" s="30" t="n"/>
       <c r="I11" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="K11" s="28" t="n">
-        <v>50</v>
+        <v>84</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="B12" s="26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="29" t="n">
         <v>28</v>
@@ -2674,7 +2674,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K12" s="29" t="n">
         <v>28</v>
@@ -2709,7 +2709,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="27" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K13" s="27" t="n">
         <v>72</v>
@@ -2744,7 +2744,7 @@
         <v>72</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K14" s="28" t="n">
         <v>64</v>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="28" t="n">
         <v>56</v>
@@ -2779,7 +2779,7 @@
         <v>18</v>
       </c>
       <c r="J15" s="29" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="K15" s="27" t="n">
         <v>94</v>
@@ -2788,421 +2788,421 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B16" s="26" t="n">
         <v>54</v>
       </c>
       <c r="C16" s="27" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>64</v>
+        <v>22</v>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>67</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="H16" s="30" t="n"/>
-      <c r="I16" s="27" t="n">
-        <v>94</v>
-      </c>
-      <c r="J16" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="K16" s="29" t="n">
-        <v>2</v>
+      <c r="I16" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B17" s="26" t="n">
         <v>53</v>
       </c>
-      <c r="C17" s="29" t="n">
-        <v>8</v>
+      <c r="C17" s="28" t="n">
+        <v>56</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>41</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>74</v>
+        <v>16</v>
+      </c>
+      <c r="G17" s="29" t="n">
+        <v>46</v>
       </c>
       <c r="H17" s="30" t="n"/>
       <c r="I17" s="28" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J17" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="K17" s="28" t="n">
-        <v>62</v>
+        <v>98</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B18" s="26" t="n">
-        <v>53</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <v>82</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>36</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>32</v>
       </c>
       <c r="H18" s="30" t="n"/>
-      <c r="I18" s="28" t="n">
-        <v>60</v>
+      <c r="I18" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>76</v>
+        <v>62</v>
+      </c>
+      <c r="K18" s="29" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B19" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="C19" s="27" t="n">
-        <v>84</v>
+      <c r="C19" s="28" t="n">
+        <v>66</v>
       </c>
       <c r="D19" s="27" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E19" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>60</v>
       </c>
       <c r="H19" s="30" t="n"/>
       <c r="I19" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="J19" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="K19" s="29" t="n">
         <v>48</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B20" s="26" t="n">
         <v>52</v>
       </c>
       <c r="C20" s="27" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>67</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>12</v>
+        <v>51</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>78</v>
       </c>
       <c r="H20" s="30" t="n"/>
       <c r="I20" s="29" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>86</v>
+        <v>18</v>
+      </c>
+      <c r="K20" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>52</v>
-      </c>
-      <c r="C21" s="27" t="n">
-        <v>92</v>
+        <v>51</v>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="D21" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="E21" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="F21" s="28" t="n">
-        <v>51</v>
+        <v>38</v>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>41</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H21" s="30" t="n"/>
-      <c r="I21" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="J21" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="K21" s="29" t="n">
-        <v>28</v>
+      <c r="I21" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="J21" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="K21" s="28" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B22" s="26" t="n">
-        <v>51</v>
-      </c>
-      <c r="C22" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="E22" s="27" t="n">
-        <v>96</v>
+        <v>50</v>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>46</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>31</v>
-      </c>
-      <c r="G22" s="28" t="n">
-        <v>64</v>
+        <v>4</v>
+      </c>
+      <c r="G22" s="29" t="n">
+        <v>44</v>
       </c>
       <c r="H22" s="30" t="n"/>
-      <c r="I22" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="J22" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" s="28" t="n">
-        <v>58</v>
+      <c r="I22" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="J22" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="K22" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B23" s="26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="D23" s="29" t="n">
-        <v>16</v>
+        <v>60</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>52</v>
       </c>
       <c r="E23" s="27" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F23" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="G23" s="29" t="n">
-        <v>46</v>
+        <v>31</v>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H23" s="30" t="n"/>
-      <c r="I23" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="J23" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="K23" s="30" t="n">
-        <v>0</v>
+      <c r="I23" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="J23" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="28" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B24" s="26" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="29" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="29" t="n">
         <v>44</v>
       </c>
+      <c r="E24" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>82</v>
+      </c>
       <c r="H24" s="30" t="n"/>
-      <c r="I24" s="27" t="n">
-        <v>88</v>
-      </c>
-      <c r="J24" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="K24" s="29" t="n">
-        <v>28</v>
+      <c r="I24" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B25" s="26" t="n">
-        <v>49</v>
-      </c>
-      <c r="C25" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="D25" s="27" t="n">
-        <v>94</v>
+        <v>48</v>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="E25" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="G25" s="28" t="n">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>82</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>84</v>
       </c>
       <c r="H25" s="30" t="n"/>
-      <c r="I25" s="29" t="n">
-        <v>48</v>
+      <c r="I25" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="K25" s="28" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B26" s="26" t="n">
-        <v>48</v>
-      </c>
-      <c r="C26" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="E26" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>84</v>
+        <v>47</v>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>69</v>
+      </c>
+      <c r="G26" s="29" t="n">
+        <v>32</v>
       </c>
       <c r="H26" s="30" t="n"/>
-      <c r="I26" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="J26" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="K26" s="28" t="n">
-        <v>56</v>
+      <c r="I26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="K26" s="27" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B27" s="26" t="n">
-        <v>48</v>
-      </c>
-      <c r="C27" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="D27" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="F27" s="28" t="n">
-        <v>69</v>
-      </c>
-      <c r="G27" s="29" t="n">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>76</v>
       </c>
       <c r="H27" s="30" t="n"/>
-      <c r="I27" s="30" t="n">
-        <v>0</v>
+      <c r="I27" s="29" t="n">
+        <v>28</v>
       </c>
       <c r="J27" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>90</v>
+        <v>76</v>
+      </c>
+      <c r="K27" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -3234,7 +3234,7 @@
         <v>34</v>
       </c>
       <c r="J28" s="27" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K28" s="29" t="n">
         <v>18</v>
@@ -3243,246 +3243,246 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B29" s="26" t="n">
         <v>46</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="D29" s="28" t="n">
-        <v>58</v>
-      </c>
-      <c r="E29" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="F29" s="27" t="n">
+        <v>48</v>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="E29" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="G29" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="H29" s="30" t="n"/>
+      <c r="I29" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="J29" s="27" t="n">
         <v>92</v>
       </c>
-      <c r="G29" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="H29" s="30" t="n"/>
-      <c r="I29" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="J29" s="27" t="n">
-        <v>72</v>
-      </c>
       <c r="K29" s="29" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B30" s="26" t="n">
         <v>45</v>
       </c>
       <c r="C30" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <v>98</v>
+        <v>14</v>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>2</v>
       </c>
       <c r="E30" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="G30" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>53</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H30" s="30" t="n"/>
+      <c r="I30" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="J30" s="28" t="n">
         <v>56</v>
       </c>
-      <c r="H30" s="30" t="n"/>
-      <c r="I30" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="J30" s="27" t="n">
-        <v>94</v>
-      </c>
-      <c r="K30" s="27" t="n">
-        <v>88</v>
+      <c r="K30" s="28" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B31" s="26" t="n">
         <v>45</v>
       </c>
       <c r="C31" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="D31" s="29" t="n">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>98</v>
       </c>
       <c r="E31" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="F31" s="28" t="n">
-        <v>63</v>
+        <v>32</v>
+      </c>
+      <c r="F31" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="G31" s="28" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H31" s="30" t="n"/>
-      <c r="I31" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="J31" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K31" s="29" t="n">
-        <v>22</v>
+      <c r="I31" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="J31" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="K31" s="27" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
         <v>45</v>
       </c>
       <c r="C32" s="29" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D32" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="E32" s="28" t="n">
-        <v>58</v>
+        <v>18</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>28</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>65</v>
-      </c>
-      <c r="G32" s="29" t="n">
-        <v>10</v>
+        <v>63</v>
+      </c>
+      <c r="G32" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H32" s="30" t="n"/>
-      <c r="I32" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="J32" s="28" t="n">
+      <c r="I32" s="28" t="n">
         <v>68</v>
       </c>
-      <c r="K32" s="27" t="n">
-        <v>74</v>
+      <c r="J32" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="K32" s="29" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B33" s="26" t="n">
         <v>45</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="D33" s="29" t="n">
         <v>48</v>
       </c>
-      <c r="D33" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="29" t="n">
-        <v>35</v>
-      </c>
-      <c r="G33" s="29" t="n">
-        <v>48</v>
+      <c r="G33" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H33" s="30" t="n"/>
-      <c r="I33" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>86</v>
+      <c r="I33" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="J33" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="K33" s="29" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B34" s="26" t="n">
         <v>44</v>
       </c>
       <c r="C34" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="E34" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="F34" s="29" t="n">
-        <v>47</v>
-      </c>
-      <c r="G34" s="29" t="n">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="F34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H34" s="30" t="n"/>
-      <c r="I34" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="J34" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="K34" s="29" t="n">
-        <v>12</v>
+      <c r="I34" s="28" t="n">
+        <v>54</v>
+      </c>
+      <c r="J34" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="K34" s="28" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B35" s="26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="D35" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="E35" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="F35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="28" t="n">
-        <v>64</v>
+        <v>14</v>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="E35" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="F35" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="G35" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="H35" s="30" t="n"/>
-      <c r="I35" s="28" t="n">
-        <v>54</v>
+      <c r="I35" s="29" t="n">
+        <v>42</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="K35" s="28" t="n">
-        <v>68</v>
+        <v>60</v>
+      </c>
+      <c r="K35" s="27" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="36">
@@ -3514,7 +3514,7 @@
         <v>52</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K36" s="29" t="n">
         <v>28</v>
@@ -3523,211 +3523,211 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B37" s="26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37" s="29" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D37" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <v>82</v>
+      </c>
+      <c r="F37" s="28" t="n">
+        <v>61</v>
+      </c>
+      <c r="G37" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="30" t="n"/>
+      <c r="I37" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E37" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="F37" s="28" t="n">
-        <v>53</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="H37" s="30" t="n"/>
-      <c r="I37" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="J37" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="K37" s="28" t="n">
-        <v>60</v>
+      <c r="J37" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="K37" s="29" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
         <v>40</v>
       </c>
       <c r="C38" s="29" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D38" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="E38" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" s="28" t="n">
-        <v>59</v>
+      <c r="F38" s="29" t="n">
+        <v>27</v>
       </c>
       <c r="G38" s="29" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H38" s="30" t="n"/>
       <c r="I38" s="28" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J38" s="27" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K38" s="29" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B39" s="26" t="n">
         <v>40</v>
       </c>
       <c r="C39" s="29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D39" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="E39" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="F39" s="28" t="n">
-        <v>61</v>
+        <v>34</v>
+      </c>
+      <c r="E39" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>98</v>
       </c>
       <c r="G39" s="29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H39" s="30" t="n"/>
       <c r="I39" s="29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="K39" s="29" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B40" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>59</v>
+      </c>
+      <c r="G40" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="C40" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="D40" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="E40" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="G40" s="29" t="n">
-        <v>4</v>
-      </c>
       <c r="H40" s="30" t="n"/>
-      <c r="I40" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="28" t="n">
-        <v>56</v>
+      <c r="I40" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="J40" s="27" t="n">
+        <v>70</v>
       </c>
       <c r="K40" s="29" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B41" s="26" t="n">
         <v>39</v>
       </c>
-      <c r="C41" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="D41" s="29" t="n">
-        <v>10</v>
+      <c r="C41" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="D41" s="27" t="n">
+        <v>80</v>
       </c>
       <c r="E41" s="29" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F41" s="29" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G41" s="29" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H41" s="30" t="n"/>
-      <c r="I41" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="J41" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="K41" s="29" t="n">
-        <v>14</v>
+      <c r="I41" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="J41" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="K41" s="27" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B42" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>46</v>
+      </c>
+      <c r="D42" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="C42" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="D42" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="E42" s="29" t="n">
-        <v>6</v>
+      <c r="E42" s="27" t="n">
+        <v>78</v>
       </c>
       <c r="F42" s="29" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="G42" s="29" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H42" s="30" t="n"/>
       <c r="I42" s="29" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K42" s="27" t="n">
-        <v>92</v>
+        <v>28</v>
+      </c>
+      <c r="K42" s="29" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="B43" s="26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" s="29" t="n">
         <v>14</v>
@@ -3759,7 +3759,7 @@
         <v>44</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K43" s="28" t="n">
         <v>54</v>
@@ -3768,71 +3768,71 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B44" s="26" t="n">
         <v>34</v>
       </c>
-      <c r="C44" s="27" t="n">
-        <v>88</v>
+      <c r="C44" s="28" t="n">
+        <v>54</v>
       </c>
       <c r="D44" s="29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E44" s="29" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F44" s="29" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G44" s="29" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H44" s="30" t="n"/>
       <c r="I44" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" s="27" t="n">
+        <v>96</v>
+      </c>
+      <c r="K44" s="29" t="n">
         <v>6</v>
-      </c>
-      <c r="J44" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="K44" s="27" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B45" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="C45" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="D45" s="30" t="n">
-        <v>0</v>
+      <c r="C45" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="D45" s="29" t="n">
+        <v>28</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F45" s="29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G45" s="29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H45" s="30" t="n"/>
       <c r="I45" s="29" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="K45" s="27" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -3864,7 +3864,7 @@
         <v>38</v>
       </c>
       <c r="J46" s="29" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K46" s="29" t="n">
         <v>28</v>
@@ -3873,36 +3873,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B47" s="26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C47" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="D47" s="29" t="n">
-        <v>32</v>
+        <v>68</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="E47" s="29" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F47" s="29" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G47" s="29" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H47" s="30" t="n"/>
       <c r="I47" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J47" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="K47" s="29" t="n">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="J47" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="K47" s="27" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="48">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="B48" s="26" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C48" s="29" t="n">
         <v>4</v>
@@ -3933,8 +3933,8 @@
       <c r="I48" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="J48" s="29" t="n">
-        <v>34</v>
+      <c r="J48" s="28" t="n">
+        <v>54</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>78</v>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="B49" s="26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C49" s="29" t="n">
         <v>22</v>
@@ -3968,8 +3968,8 @@
       <c r="I49" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="J49" s="30" t="n">
-        <v>0</v>
+      <c r="J49" s="29" t="n">
+        <v>24</v>
       </c>
       <c r="K49" s="29" t="n">
         <v>10</v>
@@ -3978,71 +3978,71 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B50" s="26" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>62</v>
+      </c>
+      <c r="E50" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="G50" s="29" t="n">
         <v>2</v>
-      </c>
-      <c r="D50" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="E50" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="F50" s="29" t="n">
-        <v>45</v>
-      </c>
-      <c r="G50" s="29" t="n">
-        <v>38</v>
       </c>
       <c r="H50" s="30" t="n"/>
       <c r="I50" s="29" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K50" s="27" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B51" s="26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C51" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="D51" s="28" t="n">
-        <v>62</v>
+        <v>2</v>
+      </c>
+      <c r="D51" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="E51" s="29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F51" s="29" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G51" s="29" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H51" s="30" t="n"/>
       <c r="I51" s="29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J51" s="29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K51" s="27" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>74 (A+)</t>
+          <t>72 (A+)</t>
         </is>
       </c>
       <c r="C2" s="30" t="n">
@@ -4172,7 +4172,7 @@
         <v>2.23</v>
       </c>
       <c r="J2" s="30" t="n">
-        <v>4.15</v>
+        <v>-5.68</v>
       </c>
       <c r="K2" s="30" t="n">
         <v>7.05</v>
@@ -4187,7 +4187,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
@@ -4196,164 +4196,164 @@
         </is>
       </c>
       <c r="C3" s="30" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D3" s="30" t="n">
-        <v>0.54</v>
+        <v>1.13</v>
       </c>
       <c r="E3" s="30" t="n">
-        <v>3.51</v>
+        <v>4.49</v>
       </c>
       <c r="F3" s="30" t="n">
-        <v>0.9</v>
+        <v>2.97</v>
       </c>
       <c r="G3" s="30" t="n">
-        <v>2.64</v>
+        <v>4.32</v>
       </c>
       <c r="H3" s="30" t="n"/>
       <c r="I3" s="30" t="n">
-        <v>0.68</v>
+        <v>2.49</v>
       </c>
       <c r="J3" s="30" t="n">
-        <v>18.86</v>
+        <v>28.2</v>
       </c>
       <c r="K3" s="30" t="n">
-        <v>7</v>
+        <v>6.97</v>
       </c>
       <c r="L3" s="30" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="M3" s="30" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>72 (A+)</t>
+          <t>71 (A+)</t>
         </is>
       </c>
       <c r="C4" s="30" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D4" s="30" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>4.49</v>
+        <v>3.51</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>2.97</v>
+        <v>0.9</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>4.32</v>
+        <v>2.64</v>
       </c>
       <c r="H4" s="30" t="n"/>
       <c r="I4" s="30" t="n">
-        <v>2.49</v>
+        <v>0.68</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>40.08</v>
+        <v>18.07</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="L4" s="30" t="n">
-        <v>-1.72</v>
+        <v>0</v>
       </c>
       <c r="M4" s="30" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>71 (A+)</t>
+          <t>69 (A+)</t>
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>8.109999999999999</v>
+        <v>7.35</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>0.95</v>
+        <v>1.38</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H5" s="30" t="n"/>
       <c r="I5" s="30" t="n">
-        <v>0.31</v>
+        <v>0.73</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>24.76</v>
+        <v>-3.34</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>8.35</v>
+        <v>7</v>
       </c>
       <c r="L5" s="30" t="n">
-        <v>13.51</v>
+        <v>0</v>
       </c>
       <c r="M5" s="30" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>70 (A+)</t>
+          <t>68 (A+)</t>
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>0.34</v>
+        <v>-0.21</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>7.35</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>1.38</v>
+        <v>0.95</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H6" s="30" t="n"/>
       <c r="I6" s="30" t="n">
-        <v>0.73</v>
+        <v>0.31</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>-5.58</v>
+        <v>-1.83</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>7</v>
+        <v>8.35</v>
       </c>
       <c r="L6" s="30" t="n">
-        <v>0</v>
+        <v>13.51</v>
       </c>
       <c r="M6" s="30" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>70 (A+)</t>
+          <t>68 (A)</t>
         </is>
       </c>
       <c r="C7" s="30" t="n">
@@ -4387,7 +4387,7 @@
         <v>1.88</v>
       </c>
       <c r="J7" s="30" t="n">
-        <v>-7.56</v>
+        <v>-26.73</v>
       </c>
       <c r="K7" s="30" t="n">
         <v>6.47</v>
@@ -4430,7 +4430,7 @@
         <v>1.54</v>
       </c>
       <c r="J8" s="30" t="n">
-        <v>-23.67</v>
+        <v>-22.75</v>
       </c>
       <c r="K8" s="30" t="n">
         <v>6.95</v>
@@ -4445,130 +4445,130 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C9" s="30" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="30" t="n">
-        <v>1.42</v>
+        <v>0.8</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>2.14</v>
+        <v>5.08</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>2.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>2.86</v>
+        <v>4.4</v>
       </c>
       <c r="H9" s="30" t="n"/>
       <c r="I9" s="30" t="n">
-        <v>0.83</v>
+        <v>1.16</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>7.73</v>
+        <v>6.88</v>
       </c>
       <c r="L9" s="30" t="n">
-        <v>9.09</v>
+        <v>1.39</v>
       </c>
       <c r="M9" s="30" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>63 (A-)</t>
+          <t>66 (A)</t>
         </is>
       </c>
       <c r="C10" s="30" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>5.08</v>
+        <v>4.21</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>4.4</v>
+        <v>3.86</v>
       </c>
       <c r="H10" s="30" t="n"/>
       <c r="I10" s="30" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>-29.04</v>
+        <v>28.53</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>6.88</v>
+        <v>7.05</v>
       </c>
       <c r="L10" s="30" t="n">
-        <v>1.39</v>
+        <v>3.57</v>
       </c>
       <c r="M10" s="30" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>61 (A-)</t>
+          <t>65 (A)</t>
         </is>
       </c>
       <c r="C11" s="30" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>0.98</v>
+        <v>1.42</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>4.21</v>
+        <v>2.14</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>3.86</v>
+        <v>2.86</v>
       </c>
       <c r="H11" s="30" t="n"/>
       <c r="I11" s="30" t="n">
-        <v>1.46</v>
+        <v>0.83</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>-9.84</v>
+        <v>16.37</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>7.05</v>
+        <v>7.73</v>
       </c>
       <c r="L11" s="30" t="n">
-        <v>3.57</v>
+        <v>9.09</v>
       </c>
       <c r="M11" s="30" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>59 (B+)</t>
+          <t>58 (B+)</t>
         </is>
       </c>
       <c r="C12" s="30" t="n">
@@ -4602,7 +4602,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>-13.44</v>
+        <v>-15.89</v>
       </c>
       <c r="K12" s="30" t="n">
         <v>7</v>
@@ -4645,7 +4645,7 @@
         <v>-0.05</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>25.84</v>
+        <v>24.71</v>
       </c>
       <c r="K13" s="30" t="n">
         <v>7.28</v>
@@ -4688,7 +4688,7 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="30" t="n">
-        <v>-11.73</v>
+        <v>-15.65</v>
       </c>
       <c r="K14" s="30" t="n">
         <v>7.26</v>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>55 (B+)</t>
         </is>
       </c>
       <c r="C15" s="30" t="n">
@@ -4731,7 +4731,7 @@
         <v>-0.47</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>-10.35</v>
+        <v>-2.34</v>
       </c>
       <c r="K15" s="30" t="n">
         <v>8.279999999999999</v>
@@ -4746,7 +4746,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
@@ -4755,41 +4755,41 @@
         </is>
       </c>
       <c r="C16" s="30" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>-0.48</v>
+        <v>-1.35</v>
       </c>
       <c r="E16" s="30" t="n">
-        <v>-0.78</v>
+        <v>4.15</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>7.4</v>
+        <v>1.63</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>2.92</v>
+        <v>0.82</v>
       </c>
       <c r="H16" s="30" t="n"/>
       <c r="I16" s="30" t="n">
-        <v>1.59</v>
+        <v>0.06</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>120.21</v>
+        <v>-14.98</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>6</v>
+        <v>7.73</v>
       </c>
       <c r="L16" s="30" t="n">
-        <v>-10</v>
+        <v>7.32</v>
       </c>
       <c r="M16" s="30" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -4798,84 +4798,84 @@
         </is>
       </c>
       <c r="C17" s="30" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>-0.77</v>
+        <v>-1.71</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>5.44</v>
+        <v>5.78</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>3.08</v>
+        <v>2.36</v>
       </c>
       <c r="H17" s="30" t="n"/>
       <c r="I17" s="30" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>93.95999999999999</v>
+        <v>118.02</v>
       </c>
       <c r="K17" s="30" t="n">
-        <v>7.23</v>
+        <v>5.44</v>
       </c>
       <c r="L17" s="30" t="n">
-        <v>2.27</v>
+        <v>-15.56</v>
       </c>
       <c r="M17" s="30" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C18" s="30" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>-0.5</v>
+        <v>0.88</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>5.13</v>
+        <v>3.11</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>3.58</v>
+        <v>2.1</v>
       </c>
       <c r="H18" s="30" t="n"/>
       <c r="I18" s="30" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>3.19</v>
+        <v>15.21</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>7.36</v>
+        <v>7.02</v>
       </c>
       <c r="L18" s="30" t="n">
-        <v>-3.9</v>
+        <v>3.51</v>
       </c>
       <c r="M18" s="30" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
@@ -4884,41 +4884,39 @@
         </is>
       </c>
       <c r="C19" s="30" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D19" s="30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E19" s="30" t="n">
         <v>0.88</v>
       </c>
-      <c r="E19" s="30" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="F19" s="30" t="n">
-        <v>1.42</v>
-      </c>
+      <c r="F19" s="30" t="n"/>
       <c r="G19" s="30" t="n">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="H19" s="30" t="n"/>
       <c r="I19" s="30" t="n">
-        <v>-0.46</v>
+        <v>0.57</v>
       </c>
       <c r="J19" s="30" t="n">
-        <v>7.37</v>
+        <v>-0.61</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>7.02</v>
+        <v>7.26</v>
       </c>
       <c r="L19" s="30" t="n">
-        <v>3.51</v>
+        <v>7.84</v>
       </c>
       <c r="M19" s="30" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
@@ -4927,334 +4925,336 @@
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>-1.35</v>
+        <v>-0.95</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>0.82</v>
+        <v>3.34</v>
       </c>
       <c r="H20" s="30" t="n"/>
       <c r="I20" s="30" t="n">
-        <v>0.06</v>
+        <v>0.65</v>
       </c>
       <c r="J20" s="30" t="n">
-        <v>-37.46</v>
+        <v>-17.83</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>7.73</v>
+        <v>7</v>
       </c>
       <c r="L20" s="30" t="n">
-        <v>7.32</v>
+        <v>1.69</v>
       </c>
       <c r="M20" s="30" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>3.92</v>
+        <v>5.44</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="H21" s="30" t="n"/>
       <c r="I21" s="30" t="n">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>-21.89</v>
+        <v>23.71</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>7</v>
+        <v>7.23</v>
       </c>
       <c r="L21" s="30" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="M21" s="30" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C22" s="30" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>-0.22</v>
+        <v>-2.18</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>7.68</v>
+        <v>3.39</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>3.13</v>
+        <v>5.93</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="H22" s="30" t="n"/>
       <c r="I22" s="30" t="n">
-        <v>0.35</v>
+        <v>1.83</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>-36.23</v>
+        <v>26.84</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>7.16</v>
+        <v>7</v>
       </c>
       <c r="L22" s="30" t="n">
-        <v>-5.56</v>
+        <v>0</v>
       </c>
       <c r="M22" s="30" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C23" s="30" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="D23" s="30" t="n">
-        <v>-1.71</v>
+        <v>-0.22</v>
       </c>
       <c r="E23" s="30" t="n">
-        <v>5.78</v>
+        <v>7.68</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="H23" s="30" t="n"/>
       <c r="I23" s="30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="J23" s="30" t="n">
-        <v>32.14</v>
+        <v>-34.1</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>5.44</v>
+        <v>7.16</v>
       </c>
       <c r="L23" s="30" t="n">
-        <v>-15.56</v>
+        <v>-5.56</v>
       </c>
       <c r="M23" s="30" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C24" s="30" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D24" s="30" t="n">
-        <v>-2.18</v>
+        <v>-0.5</v>
       </c>
       <c r="E24" s="30" t="n">
-        <v>3.39</v>
+        <v>5.13</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>5.93</v>
+        <v>1.3</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>2.32</v>
+        <v>3.58</v>
       </c>
       <c r="H24" s="30" t="n"/>
       <c r="I24" s="30" t="n">
-        <v>1.83</v>
+        <v>0.92</v>
       </c>
       <c r="J24" s="30" t="n">
-        <v>17.69</v>
+        <v>-10.1</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>7</v>
+        <v>7.36</v>
       </c>
       <c r="L24" s="30" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="M24" s="30" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C25" s="30" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>1.8</v>
+        <v>0.28</v>
       </c>
       <c r="E25" s="30" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F25" s="30" t="n"/>
+        <v>1.21</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>1.33</v>
+      </c>
       <c r="G25" s="30" t="n">
-        <v>2.86</v>
+        <v>3.62</v>
       </c>
       <c r="H25" s="30" t="n"/>
       <c r="I25" s="30" t="n">
-        <v>0.57</v>
+        <v>1.3</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>-16.61</v>
+        <v>-2.18</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>7.26</v>
+        <v>7.1</v>
       </c>
       <c r="L25" s="30" t="n">
-        <v>7.84</v>
+        <v>1.96</v>
       </c>
       <c r="M25" s="30" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C26" s="30" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>0.28</v>
+        <v>-2.2</v>
       </c>
       <c r="E26" s="30" t="n">
-        <v>1.21</v>
+        <v>5.85</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="H26" s="30" t="n"/>
       <c r="I26" s="30" t="n">
-        <v>1.3</v>
+        <v>-1.96</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>-6.61</v>
+        <v>27.36</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>7.1</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L26" s="30" t="n">
-        <v>1.96</v>
+        <v>10.26</v>
       </c>
       <c r="M26" s="30" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="D27" s="30" t="n">
-        <v>-2.2</v>
+        <v>0.1</v>
       </c>
       <c r="E27" s="30" t="n">
-        <v>5.85</v>
+        <v>3.73</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>1.58</v>
+        <v>0.95</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="H27" s="30" t="n"/>
       <c r="I27" s="30" t="n">
-        <v>-1.96</v>
+        <v>0.51</v>
       </c>
       <c r="J27" s="30" t="n">
-        <v>40.37</v>
+        <v>25.98</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>8.029999999999999</v>
+        <v>7</v>
       </c>
       <c r="L27" s="30" t="n">
-        <v>10.26</v>
+        <v>0</v>
       </c>
       <c r="M27" s="30" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
@@ -5288,7 +5288,7 @@
         <v>0.5</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>33.43</v>
+        <v>27.93</v>
       </c>
       <c r="K28" s="30" t="n">
         <v>6.91</v>
@@ -5303,7 +5303,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
@@ -5312,41 +5312,41 @@
         </is>
       </c>
       <c r="C29" s="30" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="D29" s="30" t="n">
-        <v>0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="E29" s="30" t="n">
-        <v>3.73</v>
+        <v>0.03</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>0.95</v>
+        <v>3.04</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>3.22</v>
+        <v>2.46</v>
       </c>
       <c r="H29" s="30" t="n"/>
       <c r="I29" s="30" t="n">
-        <v>0.51</v>
+        <v>0.92</v>
       </c>
       <c r="J29" s="30" t="n">
-        <v>19.22</v>
+        <v>36.73</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>7</v>
+        <v>7.01</v>
       </c>
       <c r="L29" s="30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M29" s="30" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
@@ -5355,41 +5355,41 @@
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="D30" s="30" t="n">
-        <v>2.87</v>
+        <v>-2.7</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>2.93</v>
+        <v>3.28</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>3.56</v>
+        <v>2.11</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="H30" s="30" t="n"/>
       <c r="I30" s="30" t="n">
-        <v>-0.12</v>
+        <v>0.91</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>87.23999999999999</v>
+        <v>10.99</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L30" s="30" t="n">
-        <v>13.33</v>
+        <v>-4.29</v>
       </c>
       <c r="M30" s="30" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
@@ -5398,41 +5398,41 @@
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="D31" s="30" t="n">
-        <v>-1.67</v>
+        <v>2.87</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>2.15</v>
+        <v>2.93</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>1.79</v>
+        <v>3.56</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="H31" s="30" t="n"/>
       <c r="I31" s="30" t="n">
-        <v>0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="J31" s="30" t="n">
-        <v>-17.89</v>
+        <v>72.27</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>6.97</v>
+        <v>7.8</v>
       </c>
       <c r="L31" s="30" t="n">
-        <v>-1.72</v>
+        <v>13.33</v>
       </c>
       <c r="M31" s="30" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
@@ -5441,41 +5441,41 @@
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="D32" s="30" t="n">
-        <v>-0.5</v>
+        <v>-1.67</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>0.8</v>
+        <v>2.92</v>
       </c>
       <c r="H32" s="30" t="n"/>
       <c r="I32" s="30" t="n">
-        <v>0.74</v>
+        <v>0.1</v>
       </c>
       <c r="J32" s="30" t="n">
-        <v>17.78</v>
+        <v>-19.62</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>7.33</v>
+        <v>6.97</v>
       </c>
       <c r="L32" s="30" t="n">
-        <v>10</v>
+        <v>-1.72</v>
       </c>
       <c r="M32" s="30" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
@@ -5484,41 +5484,41 @@
         </is>
       </c>
       <c r="C33" s="30" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D33" s="30" t="n">
-        <v>-1.1</v>
+        <v>-0.48</v>
       </c>
       <c r="E33" s="30" t="n">
-        <v>0.03</v>
+        <v>-0.78</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>3.04</v>
+        <v>7.4</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="H33" s="30" t="n"/>
       <c r="I33" s="30" t="n">
-        <v>0.92</v>
+        <v>1.59</v>
       </c>
       <c r="J33" s="30" t="n">
-        <v>39.5</v>
+        <v>-43.67</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>7.01</v>
+        <v>6</v>
       </c>
       <c r="L33" s="30" t="n">
-        <v>1.72</v>
+        <v>-10</v>
       </c>
       <c r="M33" s="30" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
@@ -5527,78 +5527,78 @@
         </is>
       </c>
       <c r="C34" s="30" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="D34" s="30" t="n">
-        <v>-0.91</v>
+        <v>1.69</v>
       </c>
       <c r="E34" s="30" t="n">
-        <v>5.51</v>
+        <v>3.09</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>2.47</v>
+        <v>7.47</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="H34" s="30" t="n"/>
       <c r="I34" s="30" t="n">
-        <v>-0.55</v>
+        <v>0.6</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>77.17</v>
+        <v>18.42</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>6.76</v>
+        <v>7.26</v>
       </c>
       <c r="L34" s="30" t="n">
-        <v>-2.44</v>
+        <v>2.63</v>
       </c>
       <c r="M34" s="30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>43 (C+)</t>
+          <t>44 (B-)</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
         <v>4.3</v>
       </c>
       <c r="D35" s="30" t="n">
-        <v>1.69</v>
+        <v>-0.5</v>
       </c>
       <c r="E35" s="30" t="n">
-        <v>3.09</v>
+        <v>4.2</v>
       </c>
       <c r="F35" s="30" t="n">
-        <v>7.47</v>
+        <v>1.67</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>2.92</v>
+        <v>0.8</v>
       </c>
       <c r="H35" s="30" t="n"/>
       <c r="I35" s="30" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="J35" s="30" t="n">
-        <v>5.95</v>
+        <v>14.19</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>7.26</v>
+        <v>7.33</v>
       </c>
       <c r="L35" s="30" t="n">
-        <v>2.63</v>
+        <v>10</v>
       </c>
       <c r="M35" s="30" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
@@ -5632,7 +5632,7 @@
         <v>0.7</v>
       </c>
       <c r="J36" s="30" t="n">
-        <v>-37.09</v>
+        <v>-36.38</v>
       </c>
       <c r="K36" s="30" t="n">
         <v>7</v>
@@ -5647,50 +5647,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>41 (C+)</t>
+          <t>42 (C+)</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D37" s="30" t="n">
-        <v>-2.7</v>
+        <v>-0.58</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>3.28</v>
+        <v>5.68</v>
       </c>
       <c r="F37" s="30" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="G37" s="30" t="n">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
       <c r="H37" s="30" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>0.91</v>
+        <v>-1.52</v>
       </c>
       <c r="J37" s="30" t="n">
-        <v>-18.76</v>
+        <v>32.26</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>7.2</v>
+        <v>6.99</v>
       </c>
       <c r="L37" s="30" t="n">
-        <v>-4.29</v>
+        <v>1.67</v>
       </c>
       <c r="M37" s="30" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
@@ -5699,41 +5699,41 @@
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="D38" s="30" t="n">
-        <v>-1.32</v>
+        <v>-1.92</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>0.27</v>
+        <v>2.02</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>2.28</v>
+        <v>0.78</v>
       </c>
       <c r="H38" s="30" t="n"/>
       <c r="I38" s="30" t="n">
-        <v>1.39</v>
+        <v>0.76</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>31.92</v>
+        <v>30.25</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>7</v>
+        <v>6.87</v>
       </c>
       <c r="L38" s="30" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="M38" s="30" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B39" s="31" t="inlineStr">
@@ -5742,84 +5742,84 @@
         </is>
       </c>
       <c r="C39" s="30" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="D39" s="30" t="n">
-        <v>-0.58</v>
+        <v>-0.92</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>5.68</v>
+        <v>4.52</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>1.89</v>
+        <v>0.86</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="H39" s="30" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>-1.52</v>
+        <v>-0.49</v>
       </c>
       <c r="J39" s="30" t="n">
-        <v>12.62</v>
+        <v>5.41</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>6.99</v>
+        <v>6.67</v>
       </c>
       <c r="L39" s="30" t="n">
-        <v>1.67</v>
+        <v>6.25</v>
       </c>
       <c r="M39" s="30" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="D40" s="30" t="n">
-        <v>-0.92</v>
+        <v>-1.32</v>
       </c>
       <c r="E40" s="30" t="n">
-        <v>4.52</v>
+        <v>0.27</v>
       </c>
       <c r="F40" s="30" t="n">
-        <v>0.86</v>
+        <v>1.91</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>0.5</v>
+        <v>2.28</v>
       </c>
       <c r="H40" s="30" t="n"/>
       <c r="I40" s="30" t="n">
-        <v>-0.49</v>
+        <v>1.39</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>5.95</v>
+        <v>18.45</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="L40" s="30" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="M40" s="30" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B41" s="31" t="inlineStr">
@@ -5828,78 +5828,78 @@
         </is>
       </c>
       <c r="C41" s="30" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="D41" s="30" t="n">
-        <v>-1.92</v>
+        <v>0.85</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>2.02</v>
+        <v>0.52</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>3.35</v>
+        <v>5.18</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>0.78</v>
+        <v>2.06</v>
       </c>
       <c r="H41" s="30" t="n"/>
       <c r="I41" s="30" t="n">
-        <v>0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>21.94</v>
+        <v>13.52</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>6.87</v>
+        <v>8.25</v>
       </c>
       <c r="L41" s="30" t="n">
-        <v>-1.96</v>
+        <v>12.5</v>
       </c>
       <c r="M41" s="30" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>38 (C)</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D42" s="30" t="n">
-        <v>0.85</v>
+        <v>-0.91</v>
       </c>
       <c r="E42" s="30" t="n">
-        <v>0.52</v>
+        <v>5.51</v>
       </c>
       <c r="F42" s="30" t="n">
-        <v>5.18</v>
+        <v>2.47</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="H42" s="30" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>-0.25</v>
+        <v>-0.55</v>
       </c>
       <c r="J42" s="30" t="n">
-        <v>-10.38</v>
+        <v>-10.45</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>8.25</v>
+        <v>6.76</v>
       </c>
       <c r="L42" s="30" t="n">
-        <v>12.5</v>
+        <v>-2.44</v>
       </c>
       <c r="M42" s="30" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>35 (C)</t>
+          <t>34 (C)</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
@@ -5933,7 +5933,7 @@
         <v>0.75</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>-13.3</v>
+        <v>-19.99</v>
       </c>
       <c r="K43" s="30" t="n">
         <v>7.09</v>
@@ -5948,7 +5948,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B44" s="31" t="inlineStr">
@@ -5957,41 +5957,41 @@
         </is>
       </c>
       <c r="C44" s="30" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D44" s="30" t="n">
-        <v>-0.99</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E44" s="30" t="n">
-        <v>0.58</v>
+        <v>2.4</v>
       </c>
       <c r="F44" s="30" t="n">
-        <v>4.49</v>
+        <v>3.54</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="H44" s="30" t="n"/>
       <c r="I44" s="30" t="n">
-        <v>-1.05</v>
+        <v>-0.82</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>-3.15</v>
+        <v>83.77</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>7.51</v>
+        <v>6.56</v>
       </c>
       <c r="L44" s="30" t="n">
-        <v>8.51</v>
+        <v>-4.35</v>
       </c>
       <c r="M44" s="30" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B45" s="31" t="inlineStr">
@@ -6000,35 +6000,35 @@
         </is>
       </c>
       <c r="C45" s="30" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="D45" s="30" t="n">
-        <v>-7.49</v>
+        <v>-0.99</v>
       </c>
       <c r="E45" s="30" t="n">
-        <v>1.41</v>
+        <v>0.58</v>
       </c>
       <c r="F45" s="30" t="n">
-        <v>4.59</v>
+        <v>4.49</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="H45" s="30" t="n"/>
       <c r="I45" s="30" t="n">
-        <v>0.68</v>
+        <v>-1.05</v>
       </c>
       <c r="J45" s="30" t="n">
-        <v>-3.73</v>
+        <v>-3.35</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>7.27</v>
+        <v>7.51</v>
       </c>
       <c r="L45" s="30" t="n">
-        <v>2.7</v>
+        <v>8.51</v>
       </c>
       <c r="M45" s="30" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>32 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C46" s="30" t="n">
@@ -6077,44 +6077,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>30 (C-)</t>
+          <t>32 (C)</t>
         </is>
       </c>
       <c r="C47" s="30" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="D47" s="30" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-7.49</v>
       </c>
       <c r="E47" s="30" t="n">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="F47" s="30" t="n">
-        <v>3.54</v>
+        <v>4.59</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="H47" s="30" t="n"/>
       <c r="I47" s="30" t="n">
-        <v>-0.82</v>
+        <v>0.68</v>
       </c>
       <c r="J47" s="30" t="n">
-        <v>10.33</v>
+        <v>-5.72</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>6.56</v>
+        <v>7.27</v>
       </c>
       <c r="L47" s="30" t="n">
-        <v>-4.35</v>
+        <v>2.7</v>
       </c>
       <c r="M47" s="30" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>29 (C-)</t>
+          <t>31 (C-)</t>
         </is>
       </c>
       <c r="C48" s="30" t="n">
@@ -6148,7 +6148,7 @@
         <v>0.06</v>
       </c>
       <c r="J48" s="30" t="n">
-        <v>-10.28</v>
+        <v>8.24</v>
       </c>
       <c r="K48" s="30" t="n">
         <v>7.41</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>28 (C-)</t>
+          <t>30 (C-)</t>
         </is>
       </c>
       <c r="C49" s="30" t="n">
@@ -6191,7 +6191,7 @@
         <v>0.22</v>
       </c>
       <c r="J49" s="30" t="n">
-        <v>-42.35</v>
+        <v>-15.18</v>
       </c>
       <c r="K49" s="30" t="n">
         <v>6.73</v>
@@ -6206,7 +6206,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B50" s="31" t="inlineStr">
@@ -6215,78 +6215,78 @@
         </is>
       </c>
       <c r="C50" s="30" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="D50" s="30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="E50" s="30" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>2.57</v>
+        <v>3.39</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>2.24</v>
+        <v>0.32</v>
       </c>
       <c r="H50" s="30" t="n"/>
       <c r="I50" s="30" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>-18.71</v>
+        <v>-31.05</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>7.53</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L50" s="30" t="n">
-        <v>5.26</v>
+        <v>12.82</v>
       </c>
       <c r="M50" s="30" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>27 (C-)</t>
+          <t>26 (D)</t>
         </is>
       </c>
       <c r="C51" s="30" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="D51" s="30" t="n">
-        <v>0.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E51" s="30" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="F51" s="30" t="n">
-        <v>3.39</v>
+        <v>2.57</v>
       </c>
       <c r="G51" s="30" t="n">
-        <v>0.32</v>
+        <v>2.24</v>
       </c>
       <c r="H51" s="30" t="n"/>
       <c r="I51" s="30" t="n">
-        <v>-0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="J51" s="30" t="n">
-        <v>-31.66</v>
+        <v>-32.95</v>
       </c>
       <c r="K51" s="30" t="n">
-        <v>8.279999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="L51" s="30" t="n">
-        <v>12.82</v>
+        <v>5.26</v>
       </c>
       <c r="M51" s="30" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -6368,306 +6368,306 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="n">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F2" s="14" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="G2" s="14" t="n">
+      <c r="F2" s="11" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G2" s="11" t="n">
         <v>4.3</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="11" t="n">
         <v>0.6</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="11" t="n">
         <v>1.91</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="J2" s="11" t="n">
         <v>5.05</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="D3" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Chicago-Naperville-Elgin</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="I4" s="20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J4" s="20" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Houston-Pasadena-The Woodlands</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F3" s="14" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" s="14" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="I3" s="14" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="J3" s="14" t="n">
-        <v>5.93</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Chicago-Naperville-Elgin</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G4" s="23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H4" s="23" t="n">
-        <v>-2.46</v>
-      </c>
-      <c r="I4" s="23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="J4" s="23" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="F6" s="11" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Washington-Arlington-Alexandria</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Dallas-Fort Worth-Arlington</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Houston-Pasadena-The Woodlands</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="H8" s="11" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta-Sandy Springs-Roswell</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Washington-Arlington-Alexandria</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Washington DC</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="G9" s="11" t="n">
+      <c r="F9" s="8" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G9" s="8" t="n">
         <v>3.2</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="8" t="n">
         <v>0.88</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="8" t="n">
         <v>3.11</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="8" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>63.8</v>
+        <v>65.2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>4.2</v>
@@ -6710,154 +6710,154 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="G11" s="17" t="n">
+      <c r="D11" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G11" s="11" t="n">
         <v>4.8</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="11" t="n">
         <v>-2.7</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="I11" s="11" t="n">
         <v>3.28</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="11" t="n">
         <v>2.11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="11" t="n">
         <v>45.4</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="11" t="n">
         <v>3.9</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="11" t="n">
         <v>2.87</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="11" t="n">
         <v>2.93</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="11" t="n">
         <v>3.56</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="D13" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F13" s="20" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="G13" s="20" t="n">
+      <c r="F13" s="17" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G13" s="17" t="n">
         <v>5.7</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="17" t="n">
         <v>-1.75</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="17" t="n">
         <v>5.51</v>
       </c>
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="17" t="n">
         <v>3.15</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="D14" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="G14" s="11" t="n">
+      <c r="F14" s="8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>4.4</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="8" t="n">
         <v>-1.71</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I14" s="8" t="n">
         <v>5.78</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" s="8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6876,15 +6876,15 @@
         </is>
       </c>
       <c r="D15" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>26.9</v>
+        <v>25.7</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>6</v>
@@ -6900,230 +6900,230 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="D16" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="G16" s="11" t="n">
+      <c r="F16" s="8" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="8" t="n">
         <v>-0.77</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="8" t="n">
         <v>5.44</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="8" t="n">
         <v>2.81</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="D17" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F17" s="17" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="G17" s="17" t="n">
+      <c r="F17" s="14" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G17" s="14" t="n">
         <v>4.4</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="14" t="n">
         <v>-1.32</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="14" t="n">
         <v>0.27</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="14" t="n">
         <v>1.91</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="D18" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G18" s="11" t="n">
+      <c r="F18" s="8" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" s="8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="8" t="n">
         <v>5.13</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="8" t="n">
         <v>1.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F19" s="17" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="G19" s="17" t="n">
+      <c r="F19" s="14" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="G19" s="14" t="n">
         <v>4.7</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="14" t="n">
         <v>-1.75</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="14" t="n">
         <v>7.5</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="14" t="n">
         <v>4.31</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="G20" s="14" t="n">
+      <c r="F20" s="11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G20" s="11" t="n">
         <v>4.1</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="11" t="n">
         <v>-1.67</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="11" t="n">
         <v>2.15</v>
       </c>
-      <c r="J20" s="14" t="n">
+      <c r="J20" s="11" t="n">
         <v>1.79</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="G21" s="8" t="n">
+      <c r="F21" s="5" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="5" t="n">
         <v>6.12</v>
       </c>
-      <c r="J21" s="8" t="n">
+      <c r="J21" s="5" t="n">
         <v>1.56</v>
       </c>
     </row>
@@ -7166,40 +7166,40 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="G23" s="11" t="n">
+      <c r="D23" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H23" s="5" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I23" s="5" t="n">
         <v>5.99</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J23" s="5" t="n">
         <v>1.13</v>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>3.8</v>
@@ -7242,230 +7242,230 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>46</v>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="D25" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G25" s="14" t="n">
+      <c r="F25" s="11" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G25" s="11" t="n">
         <v>4.7</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="I25" s="11" t="n">
         <v>3.73</v>
       </c>
-      <c r="J25" s="14" t="n">
+      <c r="J25" s="11" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="G26" s="5" t="n">
+      <c r="D26" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I26" s="2" t="n">
         <v>5.08</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="J26" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n">
+      <c r="A27" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F27" s="17" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="G27" s="17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="I27" s="17" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="J27" s="17" t="n">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Sacramento-Roseville-Folsom</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="G28" s="17" t="n">
+      <c r="F28" s="14" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="G28" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="17" t="n">
+      <c r="H28" s="14" t="n">
         <v>-1.92</v>
       </c>
-      <c r="I28" s="17" t="n">
+      <c r="I28" s="14" t="n">
         <v>2.02</v>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="14" t="n">
         <v>3.35</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="G29" s="8" t="n">
+      <c r="F29" s="5" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I29" s="5" t="n">
         <v>3.33</v>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="J29" s="5" t="n">
         <v>1.95</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="G30" s="5" t="n">
+      <c r="D30" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>5.4</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I30" s="2" t="n">
         <v>4.21</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J30" s="2" t="n">
         <v>2.46</v>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>3.7</v>
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>69.7</v>
+        <v>69.3</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.8</v>
@@ -7546,152 +7546,152 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Indianapolis-Carmel-Greenwood</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H33" s="11" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G34" s="20" t="n">
+      <c r="F35" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="G35" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="H34" s="20" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="I34" s="20" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J34" s="20" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H35" s="14" t="n">
+      <c r="H35" s="8" t="n">
         <v>1.8</v>
       </c>
-      <c r="I35" s="14" t="n">
+      <c r="I35" s="8" t="n">
         <v>0.88</v>
       </c>
-      <c r="J35" s="14" t="n"/>
+      <c r="J35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F36" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="G36" s="11" t="n">
+      <c r="F36" s="8" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G36" s="8" t="n">
         <v>3.1</v>
       </c>
-      <c r="H36" s="11" t="n">
+      <c r="H36" s="8" t="n">
         <v>-0.95</v>
       </c>
-      <c r="I36" s="11" t="n">
+      <c r="I36" s="8" t="n">
         <v>3.92</v>
       </c>
-      <c r="J36" s="11" t="n">
+      <c r="J36" s="8" t="n">
         <v>2.39</v>
       </c>
     </row>
@@ -7710,15 +7710,15 @@
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>54.4</v>
+        <v>44.6</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>4.1</v>
@@ -7734,154 +7734,154 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D38" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="G39" s="20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I39" s="20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J39" s="20" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Providence-Warwick</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F38" s="14" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="G38" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="J38" s="14" t="n">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>Jacksonville</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>Jacksonville</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G39" s="23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H39" s="23" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I39" s="23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J39" s="23" t="n">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="n">
+      <c r="F40" s="11" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Milwaukee-Waukesha</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Providence-Warwick</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F40" s="17" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H40" s="17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="I40" s="17" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="J40" s="17" t="n">
-        <v>7.47</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="21" t="inlineStr">
-        <is>
-          <t>Milwaukee-Waukesha</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="G41" s="20" t="n">
+      <c r="F41" s="14" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G41" s="14" t="n">
         <v>3.8</v>
       </c>
-      <c r="H41" s="20" t="n">
+      <c r="H41" s="14" t="n">
         <v>0.85</v>
       </c>
-      <c r="I41" s="20" t="n">
+      <c r="I41" s="14" t="n">
         <v>0.52</v>
       </c>
-      <c r="J41" s="20" t="n">
+      <c r="J41" s="14" t="n">
         <v>5.18</v>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>73.8</v>
+        <v>72</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3.2</v>
@@ -7924,154 +7924,154 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="n">
+      <c r="A43" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D43" s="14" t="n">
+      <c r="D43" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Louisville-Jefferson County</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I44" s="20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J44" s="20" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="G43" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J43" s="14" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>Louisville-Jefferson County</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="G44" s="23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H44" s="23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I44" s="23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J44" s="23" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H45" s="23" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="I45" s="23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J45" s="23" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F46" s="17" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="G46" s="17" t="n">
+      <c r="F46" s="14" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G46" s="14" t="n">
         <v>4.7</v>
       </c>
-      <c r="H46" s="17" t="n">
+      <c r="H46" s="14" t="n">
         <v>-0.92</v>
       </c>
-      <c r="I46" s="17" t="n">
+      <c r="I46" s="14" t="n">
         <v>4.52</v>
       </c>
-      <c r="J46" s="17" t="n">
+      <c r="J46" s="14" t="n">
         <v>0.86</v>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>72.2</v>
+        <v>71.8</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.5</v>
@@ -8114,40 +8114,40 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="n">
+      <c r="A48" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D48" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="D48" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F48" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="G48" s="14" t="n">
+      <c r="F48" s="11" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G48" s="11" t="n">
         <v>3.5</v>
       </c>
-      <c r="H48" s="14" t="n">
+      <c r="H48" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="I48" s="14" t="n">
+      <c r="I48" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="J48" s="14" t="n">
+      <c r="J48" s="11" t="n">
         <v>3.04</v>
       </c>
     </row>
@@ -8170,11 +8170,11 @@
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>32.5</v>
+        <v>31.7</v>
       </c>
       <c r="G49" s="20" t="n">
         <v>7.7</v>
@@ -8190,40 +8190,40 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n">
+      <c r="A50" s="17" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>Grand Rapids</t>
         </is>
       </c>
-      <c r="D50" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
+      <c r="D50" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F50" s="20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G50" s="20" t="n">
+      <c r="F50" s="17" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="G50" s="17" t="n">
         <v>4.3</v>
       </c>
-      <c r="H50" s="20" t="n">
+      <c r="H50" s="17" t="n">
         <v>-7.49</v>
       </c>
-      <c r="I50" s="20" t="n">
+      <c r="I50" s="17" t="n">
         <v>1.41</v>
       </c>
-      <c r="J50" s="20" t="n">
+      <c r="J50" s="17" t="n">
         <v>4.59</v>
       </c>
     </row>
@@ -8242,15 +8242,15 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>70.5</v>
+        <v>67.7</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="C3" s="36" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D3" s="36" t="inlineStr">
         <is>
@@ -8365,11 +8365,11 @@
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="G3" s="37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="C4" s="36" t="n">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="G4" s="37" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
@@ -8417,11 +8417,11 @@
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C5" s="36" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G5" s="37" t="n">
@@ -8451,11 +8451,11 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="G6" s="37" t="n">
@@ -8485,11 +8485,11 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="H7" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8523,11 +8523,11 @@
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E8" s="37" t="n">
@@ -8535,15 +8535,15 @@
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="G8" s="37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H8" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="G9" s="37" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H9" s="37" t="inlineStr">
         <is>
@@ -8587,11 +8587,11 @@
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="G10" s="37" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H10" s="37" t="inlineStr">
         <is>
@@ -8621,15 +8621,15 @@
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E11" s="37" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="G11" s="37" t="n">
@@ -8655,15 +8655,15 @@
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" s="37" t="n">
@@ -8671,15 +8671,15 @@
       </c>
       <c r="F12" s="37" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G12" s="37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
     </row>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -64,6 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D1E7DD"/>
         <bgColor rgb="00D1E7DD"/>
       </patternFill>
@@ -96,12 +102,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
         <bgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B084"/>
-        <bgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
     <fill>
@@ -212,10 +212,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -764,7 +764,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Above Average</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1020,67 +1020,67 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Orlando-Kissimmee-Sanford</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
           <t>Above Average</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Orlando-Kissimmee-Sanford</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Orlando</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Baltimore-Columbia-Towson</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Above Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Baltimore-Columbia-Towson</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Baltimore</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Above Average</t>
         </is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
@@ -1237,129 +1237,129 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
+          <t>Above Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Seattle-Tacoma-Bellevue</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
           <t>Average</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Seattle-Tacoma-Bellevue</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles-Long Beach-Anaheim</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="F22" s="11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n">
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F23" s="11" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Tampa-St. Petersburg-Clearwater</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>50.3</v>
       </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F25" s="11" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F26" s="11" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F27" s="11" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F28" s="11" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F29" s="11" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F30" s="11" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F31" s="11" t="n">
@@ -1578,129 +1578,129 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Denver-Aurora-Centennial</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
           <t>Below Average</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Denver-Aurora-Centennial</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="n">
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="F33" s="14" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Below Average</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>San Jose</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Providence-Warwick</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="F34" s="14" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
         <is>
           <t>Below Average</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Providence-Warwick</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="n">
+    <row r="35">
+      <c r="A35" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F34" s="11" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="14" t="n">
         <v>44.2</v>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>Below Average</t>
         </is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F36" s="14" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F37" s="14" t="n">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F38" s="14" t="n">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F39" s="14" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F40" s="14" t="n">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F41" s="14" t="n">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F42" s="17" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="G42" s="18" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F43" s="17" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G43" s="18" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F44" s="17" t="n">
@@ -1981,36 +1981,36 @@
       </c>
       <c r="G44" s="18" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="n">
+      <c r="A45" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D45" s="19" t="n">
+      <c r="D45" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="E45" s="18" t="inlineStr">
+      <c r="E45" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F45" s="17" t="n">
+      <c r="F45" s="20" t="n">
         <v>32.8</v>
       </c>
-      <c r="G45" s="18" t="inlineStr">
+      <c r="G45" s="21" t="inlineStr">
         <is>
           <t>Very Poor</t>
         </is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
@@ -2043,36 +2043,36 @@
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n">
+      <c r="A47" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids</t>
         </is>
       </c>
-      <c r="D47" s="19" t="n">
+      <c r="D47" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="E47" s="18" t="inlineStr">
+      <c r="E47" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F47" s="17" t="n">
+      <c r="F47" s="20" t="n">
         <v>32.1</v>
       </c>
-      <c r="G47" s="18" t="inlineStr">
+      <c r="G47" s="21" t="inlineStr">
         <is>
           <t>Very Poor</t>
         </is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G49" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E50" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G50" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F51" s="23" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>69 (A+)</t>
+          <t>69 (A)</t>
         </is>
       </c>
       <c r="C5" s="30" t="n">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>68 (A+)</t>
+          <t>68 (A)</t>
         </is>
       </c>
       <c r="C6" s="30" t="n">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>58 (A-)</t>
         </is>
       </c>
       <c r="C12" s="30" t="n">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>58 (A-)</t>
         </is>
       </c>
       <c r="C13" s="30" t="n">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>54 (B+)</t>
         </is>
       </c>
       <c r="C16" s="30" t="n">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>53 (B+)</t>
         </is>
       </c>
       <c r="C17" s="30" t="n">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>52 (B+)</t>
         </is>
       </c>
       <c r="C18" s="30" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>52 (B+)</t>
         </is>
       </c>
       <c r="C19" s="30" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>52 (B+)</t>
         </is>
       </c>
       <c r="C20" s="30" t="n">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>48 (B)</t>
         </is>
       </c>
       <c r="C25" s="30" t="n">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>47 (B)</t>
         </is>
       </c>
       <c r="C26" s="30" t="n">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>47 (B)</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>46 (B)</t>
         </is>
       </c>
       <c r="C28" s="30" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>46 (B)</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (B)</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (B)</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>42 (B-)</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>42 (B-)</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>40 (B-)</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>40 (B-)</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>39 (B-)</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>39 (B-)</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>38 (C)</t>
+          <t>38 (C+)</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>34 (C+)</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>34 (C+)</t>
         </is>
       </c>
       <c r="C44" s="30" t="n">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>32 (C-)</t>
+          <t>32 (C)</t>
         </is>
       </c>
       <c r="C46" s="30" t="n">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>31 (C-)</t>
+          <t>31 (C)</t>
         </is>
       </c>
       <c r="C48" s="30" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>30 (C-)</t>
+          <t>30 (C)</t>
         </is>
       </c>
       <c r="C49" s="30" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>27 (C-)</t>
+          <t>27 (C)</t>
         </is>
       </c>
       <c r="C50" s="30" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>26 (D)</t>
+          <t>26 (C-)</t>
         </is>
       </c>
       <c r="C51" s="30" t="n">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F2" s="11" t="n">
@@ -6406,40 +6406,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="11" t="n">
         <v>50.3</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="11" t="n">
         <v>-2.18</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="11" t="n">
         <v>3.39</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="11" t="n">
         <v>5.93</v>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F4" s="20" t="n">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F6" s="11" t="n">
@@ -6558,40 +6558,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="11" t="n">
         <v>50.5</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="11" t="n">
         <v>3.7</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="11" t="n">
         <v>-0.22</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="11" t="n">
         <v>7.68</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="11" t="n">
         <v>3.13</v>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F8" s="11" t="n">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F11" s="11" t="n">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F12" s="11" t="n">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F13" s="17" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
@@ -6900,40 +6900,40 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="11" t="n">
         <v>50.7</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="11" t="n">
         <v>-0.77</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="11" t="n">
         <v>5.44</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="J16" s="11" t="n">
         <v>2.81</v>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F17" s="14" t="n">
@@ -6976,40 +6976,40 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="11" t="n">
         <v>50.3</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="11" t="n">
         <v>4.8</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="11" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="11" t="n">
         <v>5.13</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="J18" s="11" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F19" s="14" t="n">
@@ -7052,78 +7052,78 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="14" t="n">
         <v>44.8</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="14" t="n">
         <v>4.1</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" s="14" t="n">
         <v>-1.67</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="14" t="n">
         <v>2.15</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="14" t="n">
         <v>1.79</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="8" t="n">
         <v>56.6</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="8" t="n">
         <v>4.7</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="8" t="n">
         <v>0.22</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I21" s="8" t="n">
         <v>6.12</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J21" s="8" t="n">
         <v>1.56</v>
       </c>
     </row>
@@ -7166,40 +7166,40 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="8" t="n">
         <v>4.2</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="8" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I23" s="8" t="n">
         <v>5.99</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="8" t="n">
         <v>1.13</v>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F25" s="11" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F27" s="14" t="n">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F28" s="14" t="n">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
@@ -7584,40 +7584,40 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="n">
+      <c r="A34" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="20" t="n">
         <v>32.8</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="20" t="n">
         <v>3.4</v>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H34" s="20" t="n">
         <v>-0.99</v>
       </c>
-      <c r="I34" s="17" t="n">
+      <c r="I34" s="20" t="n">
         <v>0.58</v>
       </c>
-      <c r="J34" s="17" t="n">
+      <c r="J34" s="20" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F35" s="8" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
@@ -7696,40 +7696,40 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>San Jose</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="14" t="n">
         <v>44.6</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="14" t="n">
         <v>4.1</v>
       </c>
-      <c r="H37" s="11" t="n">
+      <c r="H37" s="14" t="n">
         <v>-0.48</v>
       </c>
-      <c r="I37" s="11" t="n">
+      <c r="I37" s="14" t="n">
         <v>-0.78</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J37" s="14" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F38" s="17" t="n">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
@@ -7810,40 +7810,40 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Providence-Warwick</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="14" t="n">
         <v>44.3</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H40" s="11" t="n">
+      <c r="H40" s="14" t="n">
         <v>1.69</v>
       </c>
-      <c r="I40" s="11" t="n">
+      <c r="I40" s="14" t="n">
         <v>3.09</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="J40" s="14" t="n">
         <v>7.47</v>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F41" s="14" t="n">
@@ -7924,40 +7924,40 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="14" t="n">
         <v>44.2</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H43" s="14" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="14" t="n">
         <v>4.2</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="J43" s="14" t="n">
         <v>1.67</v>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F44" s="20" t="n">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F45" s="17" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F46" s="14" t="n">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F48" s="11" t="n">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
@@ -8190,40 +8190,40 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="n">
+      <c r="A50" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids</t>
         </is>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E50" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F50" s="17" t="n">
+      <c r="F50" s="20" t="n">
         <v>32.1</v>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="G50" s="20" t="n">
         <v>4.3</v>
       </c>
-      <c r="H50" s="17" t="n">
+      <c r="H50" s="20" t="n">
         <v>-7.49</v>
       </c>
-      <c r="I50" s="17" t="n">
+      <c r="I50" s="20" t="n">
         <v>1.41</v>
       </c>
-      <c r="J50" s="17" t="n">
+      <c r="J50" s="20" t="n">
         <v>4.59</v>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E6" s="37" t="n">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" s="37" t="n">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="H7" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="H9" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="H10" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="H11" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="H12" s="37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C-</t>
         </is>
       </c>
     </row>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -70,12 +70,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1E7DD"/>
-        <bgColor rgb="00D1E7DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2F0E1"/>
         <bgColor rgb="00E2F0E1"/>
       </patternFill>
@@ -102,6 +96,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
         <bgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B084"/>
+        <bgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
     <fill>
@@ -212,10 +212,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -702,7 +702,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -808,219 +808,219 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Hartford</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>67.7</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>65.2</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>58.3</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>58.1</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Above Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
@@ -1082,162 +1082,162 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Above Average</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="13" t="n">
         <v>54</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>54.1</v>
       </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
         <v>52.3</v>
       </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>52.4</v>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F21" s="11" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F22" s="11" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F23" s="11" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F24" s="11" t="n">
@@ -1361,224 +1361,224 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
         <v>47.8</v>
       </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>Washington DC</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="16" t="n">
         <v>47</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="n">
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
         <v>47.3</v>
       </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="16" t="n">
         <v>47</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
         <v>46.6</v>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="16" t="n">
         <v>46</v>
       </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n">
         <v>45.6</v>
       </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="16" t="n">
         <v>46</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="n">
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="n">
         <v>45.6</v>
       </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="n">
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="n">
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F32" s="14" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F33" s="14" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F34" s="14" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F35" s="14" t="n">
@@ -1702,286 +1702,286 @@
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>Below Average</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n">
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="n">
         <v>41.6</v>
       </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="n">
         <v>42.4</v>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Sacramento</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
         <v>40.2</v>
       </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n">
+      <c r="A39" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n">
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="n">
         <v>40.1</v>
       </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n">
+      <c r="A40" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n">
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
         <v>39.4</v>
       </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n">
+      <c r="A41" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee-Waukesha</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="n">
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="n">
         <v>39.2</v>
       </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="n">
+      <c r="A42" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D42" s="19" t="n">
+      <c r="D42" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="n">
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="n">
         <v>37.8</v>
       </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n">
+      <c r="A43" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D43" s="19" t="n">
+      <c r="D43" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="n">
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="n">
         <v>34.2</v>
       </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n">
+      <c r="A44" s="20" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="D44" s="19" t="n">
+      <c r="D44" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="n">
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="n">
         <v>33.8</v>
       </c>
-      <c r="G44" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
@@ -2105,69 +2105,69 @@
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
-          <t>Very Poor</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="n">
+      <c r="A49" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B49" s="24" t="inlineStr">
         <is>
           <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="D49" s="22" t="n">
+      <c r="D49" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="E49" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="n">
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="n">
         <v>29.9</v>
       </c>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n">
+      <c r="A50" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>Louisville-Jefferson County</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>Louisville</t>
         </is>
       </c>
-      <c r="D50" s="22" t="n">
+      <c r="D50" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F50" s="20" t="n">
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="G50" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F51" s="23" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>72 (A+)</t>
+          <t>72 (A)</t>
         </is>
       </c>
       <c r="C3" s="30" t="n">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>71 (A+)</t>
+          <t>71 (A)</t>
         </is>
       </c>
       <c r="C4" s="30" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>68 (A)</t>
+          <t>68 (A-)</t>
         </is>
       </c>
       <c r="C7" s="30" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>67 (A)</t>
+          <t>67 (A-)</t>
         </is>
       </c>
       <c r="C8" s="30" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>67 (A)</t>
+          <t>67 (A-)</t>
         </is>
       </c>
       <c r="C9" s="30" t="n">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>66 (A)</t>
+          <t>66 (A-)</t>
         </is>
       </c>
       <c r="C10" s="30" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>65 (A-)</t>
         </is>
       </c>
       <c r="C11" s="30" t="n">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>58 (A-)</t>
+          <t>58 (B)</t>
         </is>
       </c>
       <c r="C12" s="30" t="n">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>58 (A-)</t>
+          <t>58 (B)</t>
         </is>
       </c>
       <c r="C13" s="30" t="n">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>57 (B)</t>
         </is>
       </c>
       <c r="C14" s="30" t="n">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>55 (B+)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C15" s="30" t="n">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>54 (B+)</t>
+          <t>54 (B-)</t>
         </is>
       </c>
       <c r="C16" s="30" t="n">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>53 (B+)</t>
+          <t>53 (B-)</t>
         </is>
       </c>
       <c r="C17" s="30" t="n">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>52 (B+)</t>
+          <t>52 (B-)</t>
         </is>
       </c>
       <c r="C18" s="30" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>52 (B+)</t>
+          <t>52 (B-)</t>
         </is>
       </c>
       <c r="C19" s="30" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>52 (B+)</t>
+          <t>52 (B-)</t>
         </is>
       </c>
       <c r="C20" s="30" t="n">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>51 (B-)</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C22" s="30" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C23" s="30" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C24" s="30" t="n">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>48 (B)</t>
+          <t>48 (C+)</t>
         </is>
       </c>
       <c r="C25" s="30" t="n">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>47 (B)</t>
+          <t>47 (C+)</t>
         </is>
       </c>
       <c r="C26" s="30" t="n">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>47 (B)</t>
+          <t>47 (C+)</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>46 (B)</t>
+          <t>46 (C+)</t>
         </is>
       </c>
       <c r="C28" s="30" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>46 (B)</t>
+          <t>46 (C+)</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>45 (B)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>45 (B)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>42 (B-)</t>
+          <t>42 (C)</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>42 (B-)</t>
+          <t>42 (C)</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>40 (B-)</t>
+          <t>40 (C)</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>40 (B-)</t>
+          <t>40 (C)</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>39 (B-)</t>
+          <t>39 (C)</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>39 (B-)</t>
+          <t>39 (C)</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>38 (C+)</t>
+          <t>38 (C-)</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>34 (C+)</t>
+          <t>34 (C-)</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>34 (C+)</t>
+          <t>34 (C-)</t>
         </is>
       </c>
       <c r="C44" s="30" t="n">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B45" s="31" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>33 (C-)</t>
         </is>
       </c>
       <c r="C45" s="30" t="n">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>32 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C46" s="30" t="n">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>32 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C47" s="30" t="n">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>31 (C)</t>
+          <t>31 (C-)</t>
         </is>
       </c>
       <c r="C48" s="30" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>30 (C)</t>
+          <t>30 (D)</t>
         </is>
       </c>
       <c r="C49" s="30" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>27 (C)</t>
+          <t>27 (D)</t>
         </is>
       </c>
       <c r="C50" s="30" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>26 (C-)</t>
+          <t>26 (D)</t>
         </is>
       </c>
       <c r="C51" s="30" t="n">
@@ -6368,40 +6368,40 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n">
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="n">
         <v>45.6</v>
       </c>
-      <c r="G2" s="11" t="n">
+      <c r="G2" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H2" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="I2" s="11" t="n">
+      <c r="I2" s="14" t="n">
         <v>1.91</v>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="J2" s="14" t="n">
         <v>5.05</v>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F3" s="11" t="n">
@@ -6444,116 +6444,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="n">
+      <c r="A4" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="n">
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="n">
         <v>29.9</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="23" t="n">
         <v>4.9</v>
       </c>
-      <c r="H4" s="20" t="n">
+      <c r="H4" s="23" t="n">
         <v>-2.46</v>
       </c>
-      <c r="I4" s="20" t="n">
+      <c r="I4" s="23" t="n">
         <v>3.28</v>
       </c>
-      <c r="J4" s="20" t="n">
+      <c r="J4" s="23" t="n">
         <v>3.65</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>58.3</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="8" t="n">
         <v>4.6</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="8" t="n">
         <v>0.79</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="8" t="n">
         <v>4.03</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="8" t="n">
         <v>1.22</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
         <v>47.8</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="14" t="n">
         <v>5.1</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="14" t="n">
         <v>0.28</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="14" t="n">
         <v>1.21</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="14" t="n">
         <v>1.33</v>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
@@ -6596,268 +6596,268 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Washington DC</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="n">
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n">
         <v>47.3</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="14" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="14" t="n">
         <v>5.85</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="14" t="n">
         <v>1.58</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>52.3</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G9" s="11" t="n">
         <v>3.2</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="11" t="n">
         <v>0.88</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="11" t="n">
         <v>3.11</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="J9" s="11" t="n">
         <v>1.42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>65.2</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="5" t="n">
         <v>1.42</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="5" t="n">
         <v>2.14</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="5" t="n">
         <v>2.83</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="14" t="n">
         <v>-2.7</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="14" t="n">
         <v>3.28</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="14" t="n">
         <v>2.11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="14" t="n">
         <v>3.9</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="14" t="n">
         <v>2.87</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="14" t="n">
         <v>2.93</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="14" t="n">
         <v>3.56</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n">
+      <c r="A13" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="n">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="n">
         <v>34.2</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="20" t="n">
         <v>5.7</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="20" t="n">
         <v>-1.75</v>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="20" t="n">
         <v>5.51</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="20" t="n">
         <v>3.15</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="11" t="n">
         <v>4.4</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="11" t="n">
         <v>-1.71</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="11" t="n">
         <v>5.78</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F16" s="11" t="n">
@@ -6938,40 +6938,40 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n">
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="n">
         <v>39.4</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="17" t="n">
         <v>4.4</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H17" s="17" t="n">
         <v>-1.32</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="I17" s="17" t="n">
         <v>0.27</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="17" t="n">
         <v>1.91</v>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="F18" s="11" t="n">
@@ -7014,40 +7014,40 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>42</v>
       </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="n">
         <v>41.6</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="17" t="n">
         <v>4.7</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="17" t="n">
         <v>-1.75</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="17" t="n">
         <v>7.5</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="17" t="n">
         <v>4.31</v>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F20" s="14" t="n">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
@@ -7128,40 +7128,40 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G22" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="5" t="n">
         <v>-0.7</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" s="5" t="n">
         <v>4.22</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="5" t="n">
         <v>1.45</v>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -7242,230 +7242,230 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Austin-Round Rock-San Marcos</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Portland-Vancouver-Hillsboro</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F25" s="11" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Portland-Vancouver-Hillsboro</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>42</v>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="J27" s="14" t="n">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Sacramento-Roseville-Folsom</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="8" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Las Vegas</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
+      <c r="F30" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="G30" s="2" t="n">
+      <c r="G30" s="5" t="n">
         <v>5.4</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="5" t="n">
         <v>0.98</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" s="5" t="n">
         <v>4.21</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="5" t="n">
         <v>2.46</v>
       </c>
     </row>
@@ -7546,40 +7546,40 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n">
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="n">
         <v>54.1</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="11" t="n">
         <v>3.2</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="11" t="n">
         <v>-1.35</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="11" t="n">
         <v>4.15</v>
       </c>
-      <c r="J33" s="8" t="n">
+      <c r="J33" s="11" t="n">
         <v>1.63</v>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F34" s="20" t="n">
@@ -7622,76 +7622,76 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n">
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="11" t="n">
         <v>1.8</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" s="11" t="n">
         <v>0.88</v>
       </c>
-      <c r="J35" s="8" t="n"/>
+      <c r="J35" s="11" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n">
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="n">
         <v>52.4</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="11" t="n">
         <v>3.1</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="11" t="n">
         <v>-0.95</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="I36" s="11" t="n">
         <v>3.92</v>
       </c>
-      <c r="J36" s="8" t="n">
+      <c r="J36" s="11" t="n">
         <v>2.39</v>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F37" s="14" t="n">
@@ -7734,40 +7734,40 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="n">
         <v>37.8</v>
       </c>
-      <c r="G38" s="17" t="n">
+      <c r="G38" s="20" t="n">
         <v>3.9</v>
       </c>
-      <c r="H38" s="17" t="n">
+      <c r="H38" s="20" t="n">
         <v>-0.91</v>
       </c>
-      <c r="I38" s="17" t="n">
+      <c r="I38" s="20" t="n">
         <v>5.51</v>
       </c>
-      <c r="J38" s="17" t="n">
+      <c r="J38" s="20" t="n">
         <v>2.47</v>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F40" s="14" t="n">
@@ -7848,40 +7848,40 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n">
+      <c r="A41" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee-Waukesha</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="n">
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="n">
         <v>39.2</v>
       </c>
-      <c r="G41" s="14" t="n">
+      <c r="G41" s="17" t="n">
         <v>3.8</v>
       </c>
-      <c r="H41" s="14" t="n">
+      <c r="H41" s="17" t="n">
         <v>0.85</v>
       </c>
-      <c r="I41" s="14" t="n">
+      <c r="I41" s="17" t="n">
         <v>0.52</v>
       </c>
-      <c r="J41" s="14" t="n">
+      <c r="J41" s="17" t="n">
         <v>5.18</v>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F43" s="14" t="n">
@@ -7962,116 +7962,116 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n">
+      <c r="A44" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>Louisville-Jefferson County</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Louisville</t>
         </is>
       </c>
-      <c r="D44" s="20" t="n">
+      <c r="D44" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I45" s="20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J45" s="20" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F44" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J44" s="20" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H45" s="17" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="I45" s="17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J45" s="17" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="n">
+      <c r="F46" s="17" t="n">
         <v>40.1</v>
       </c>
-      <c r="G46" s="14" t="n">
+      <c r="G46" s="17" t="n">
         <v>4.7</v>
       </c>
-      <c r="H46" s="14" t="n">
+      <c r="H46" s="17" t="n">
         <v>-0.92</v>
       </c>
-      <c r="I46" s="14" t="n">
+      <c r="I46" s="17" t="n">
         <v>4.52</v>
       </c>
-      <c r="J46" s="14" t="n">
+      <c r="J46" s="17" t="n">
         <v>0.86</v>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -8114,40 +8114,40 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n">
+      <c r="A48" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="n">
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
         <v>45.6</v>
       </c>
-      <c r="G48" s="11" t="n">
+      <c r="G48" s="14" t="n">
         <v>3.5</v>
       </c>
-      <c r="H48" s="11" t="n">
+      <c r="H48" s="14" t="n">
         <v>-1.1</v>
       </c>
-      <c r="I48" s="11" t="n">
+      <c r="I48" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="J48" s="14" t="n">
         <v>3.04</v>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E50" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
@@ -8228,40 +8228,40 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Hartford</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
         <v>67.7</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="5" t="n">
         <v>2.77</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I51" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="5" t="n">
         <v>3.12</v>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" s="37" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" s="37" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="H7" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E8" s="37" t="n">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="H8" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E9" s="37" t="n">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="H9" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E10" s="37" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="H10" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E11" s="37" t="n">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="H11" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E12" s="37" t="n">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="H12" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
     </row>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -64,8 +64,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1E7DD"/>
-        <bgColor rgb="00D1E7DD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -702,7 +702,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -803,1216 +803,1216 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Hartford</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>67.7</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>65.2</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>58.3</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>58.1</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>56.6</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="13" t="n">
         <v>54</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>54.1</v>
       </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
         <v>52.3</v>
       </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>52.4</v>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n">
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
         <v>50.7</v>
       </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>50.3</v>
       </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="n">
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>50.5</v>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n">
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>50.3</v>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
         <v>47.8</v>
       </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>Washington DC</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="16" t="n">
         <v>47</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="n">
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
         <v>47.3</v>
       </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="16" t="n">
         <v>47</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
         <v>46.6</v>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="16" t="n">
         <v>46</v>
       </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n">
         <v>45.6</v>
       </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="16" t="n">
         <v>46</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="n">
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="n">
         <v>45.6</v>
       </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="n">
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="n">
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="n">
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
         <v>44.8</v>
       </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>San Jose</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="n">
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
         <v>44.6</v>
       </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Providence-Warwick</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="n">
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n">
         <v>44.3</v>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="n">
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="n">
         <v>44.2</v>
       </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n">
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="n">
         <v>41.6</v>
       </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="n">
         <v>42.4</v>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Sacramento</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
         <v>40.2</v>
       </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n">
+      <c r="A39" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n">
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="n">
         <v>40.1</v>
       </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n">
+      <c r="A40" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n">
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
         <v>39.4</v>
       </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n">
+      <c r="A41" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee-Waukesha</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="n">
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="n">
         <v>39.2</v>
       </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="n">
+      <c r="A42" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D42" s="19" t="n">
+      <c r="D42" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="n">
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="n">
         <v>37.8</v>
       </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n">
+      <c r="A43" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D43" s="19" t="n">
+      <c r="D43" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="n">
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="n">
         <v>34.2</v>
       </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n">
+      <c r="A44" s="20" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="D44" s="19" t="n">
+      <c r="D44" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="n">
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="n">
         <v>33.8</v>
       </c>
-      <c r="G44" s="18" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="n">
+      <c r="A45" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D45" s="19" t="n">
+      <c r="D45" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="n">
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="n">
         <v>32.8</v>
       </c>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2048,33 +2048,33 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n">
+      <c r="A47" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids</t>
         </is>
       </c>
-      <c r="D47" s="19" t="n">
+      <c r="D47" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="n">
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="n">
         <v>32.1</v>
       </c>
-      <c r="G47" s="18" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2110,64 +2110,64 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="n">
+      <c r="A49" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B49" s="24" t="inlineStr">
         <is>
           <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="D49" s="22" t="n">
+      <c r="D49" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="E49" s="21" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="n">
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="n">
         <v>29.9</v>
       </c>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n">
+      <c r="A50" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>Louisville-Jefferson County</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>Louisville</t>
         </is>
       </c>
-      <c r="D50" s="22" t="n">
+      <c r="D50" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F50" s="20" t="n">
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="G50" s="21" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>72 (A+)</t>
+          <t>72 (A)</t>
         </is>
       </c>
       <c r="C3" s="30" t="n">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>71 (A+)</t>
+          <t>71 (A)</t>
         </is>
       </c>
       <c r="C4" s="30" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>69 (A+)</t>
+          <t>69 (A)</t>
         </is>
       </c>
       <c r="C5" s="30" t="n">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>68 (A+)</t>
+          <t>68 (A)</t>
         </is>
       </c>
       <c r="C6" s="30" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>68 (A)</t>
+          <t>68 (A-)</t>
         </is>
       </c>
       <c r="C7" s="30" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>67 (A)</t>
+          <t>67 (A-)</t>
         </is>
       </c>
       <c r="C8" s="30" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>67 (A)</t>
+          <t>67 (A-)</t>
         </is>
       </c>
       <c r="C9" s="30" t="n">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>66 (A)</t>
+          <t>66 (A-)</t>
         </is>
       </c>
       <c r="C10" s="30" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>65 (A-)</t>
         </is>
       </c>
       <c r="C11" s="30" t="n">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>58 (B)</t>
         </is>
       </c>
       <c r="C12" s="30" t="n">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>58 (B)</t>
         </is>
       </c>
       <c r="C13" s="30" t="n">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>57 (B)</t>
         </is>
       </c>
       <c r="C14" s="30" t="n">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>55 (B+)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C15" s="30" t="n">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>54 (B-)</t>
         </is>
       </c>
       <c r="C16" s="30" t="n">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>53 (B-)</t>
         </is>
       </c>
       <c r="C17" s="30" t="n">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>52 (B-)</t>
         </is>
       </c>
       <c r="C18" s="30" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>52 (B-)</t>
         </is>
       </c>
       <c r="C19" s="30" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>52 (B-)</t>
         </is>
       </c>
       <c r="C20" s="30" t="n">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>51 (B-)</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C22" s="30" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C23" s="30" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C24" s="30" t="n">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>48 (C+)</t>
         </is>
       </c>
       <c r="C25" s="30" t="n">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>47 (C+)</t>
         </is>
       </c>
       <c r="C26" s="30" t="n">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>47 (C+)</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>46 (C+)</t>
         </is>
       </c>
       <c r="C28" s="30" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>46 (C+)</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>45 (C+)</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>42 (C)</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>42 (C)</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>40 (C)</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>40 (C)</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>39 (C)</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>39 (C)</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>38 (C)</t>
+          <t>38 (C-)</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>34 (C-)</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>34 (C-)</t>
         </is>
       </c>
       <c r="C44" s="30" t="n">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B45" s="31" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>33 (C-)</t>
         </is>
       </c>
       <c r="C45" s="30" t="n">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>32 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C47" s="30" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>30 (C-)</t>
+          <t>30 (D)</t>
         </is>
       </c>
       <c r="C49" s="30" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>27 (C-)</t>
+          <t>27 (D)</t>
         </is>
       </c>
       <c r="C50" s="30" t="n">
@@ -6368,496 +6368,496 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles-Long Beach-Anaheim</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H2" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I2" s="11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J2" s="11" t="n">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
+      <c r="F3" s="11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Chicago-Naperville-Elgin</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="I4" s="23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J4" s="23" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Houston-Pasadena-The Woodlands</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>5.93</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Chicago-Naperville-Elgin</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Washington-Arlington-Alexandria</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta-Sandy Springs-Roswell</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Phoenix-Mesa-Chandler</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Boston-Cambridge-Newton</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Riverside-San Bernardino-Ontario</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>C-</t>
         </is>
       </c>
-      <c r="F4" s="20" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H4" s="20" t="n">
-        <v>-2.46</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Dallas-Fort Worth-Arlington</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Houston-Pasadena-The Woodlands</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F13" s="20" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco-Oakland-Fremont</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Washington-Arlington-Alexandria</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Washington DC</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Philadelphia-Camden-Wilmington</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Phoenix-Mesa-Chandler</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Boston-Cambridge-Newton</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Riverside-San Bernardino-Ontario</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco-Oakland-Fremont</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="11" t="n">
         <v>4.4</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="11" t="n">
         <v>-1.71</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="11" t="n">
         <v>5.78</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6900,306 +6900,306 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Minneapolis-St. Paul-Bloomington</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Tampa-St. Petersburg-Clearwater</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>San Diego-Chula Vista-Carlsbad</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Denver-Aurora-Centennial</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Orlando-Kissimmee-Sanford</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="F21" s="8" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte-Concord-Gastonia</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Baltimore-Columbia-Towson</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>42</v>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Denver-Aurora-Centennial</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Orlando-Kissimmee-Sanford</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Orlando</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Charlotte-Concord-Gastonia</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Baltimore-Columbia-Towson</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Baltimore</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
+      <c r="F23" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="8" t="n">
         <v>4.2</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="8" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I23" s="8" t="n">
         <v>5.99</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="8" t="n">
         <v>1.13</v>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -7242,230 +7242,230 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
         <v>46.6</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" s="14" t="n">
         <v>4.7</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H25" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I25" s="14" t="n">
         <v>3.73</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J25" s="14" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="5" t="n">
         <v>5.08</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>42</v>
       </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="n">
         <v>42.4</v>
       </c>
-      <c r="G27" s="14" t="n">
+      <c r="G27" s="17" t="n">
         <v>4.9</v>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="H27" s="17" t="n">
         <v>-0.58</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="I27" s="17" t="n">
         <v>5.68</v>
       </c>
-      <c r="J27" s="14" t="n">
+      <c r="J27" s="17" t="n">
         <v>1.89</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>Sacramento</t>
         </is>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n">
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="n">
         <v>40.2</v>
       </c>
-      <c r="G28" s="14" t="n">
+      <c r="G28" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="17" t="n">
         <v>-1.92</v>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="I28" s="17" t="n">
         <v>2.02</v>
       </c>
-      <c r="J28" s="14" t="n">
+      <c r="J28" s="17" t="n">
         <v>3.35</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>58.1</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="8" t="n">
         <v>3.7</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="8" t="n">
         <v>1.61</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I29" s="8" t="n">
         <v>3.33</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="8" t="n">
         <v>1.95</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G30" s="5" t="n">
         <v>5.4</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="5" t="n">
         <v>0.98</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" s="5" t="n">
         <v>4.21</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="5" t="n">
         <v>2.46</v>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -7546,228 +7546,228 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n">
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="n">
         <v>54.1</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="11" t="n">
         <v>3.2</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="11" t="n">
         <v>-1.35</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="11" t="n">
         <v>4.15</v>
       </c>
-      <c r="J33" s="8" t="n">
+      <c r="J33" s="11" t="n">
         <v>1.63</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="n">
+      <c r="A34" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="n">
         <v>32.8</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="20" t="n">
         <v>3.4</v>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H34" s="20" t="n">
         <v>-0.99</v>
       </c>
-      <c r="I34" s="17" t="n">
+      <c r="I34" s="20" t="n">
         <v>0.58</v>
       </c>
-      <c r="J34" s="17" t="n">
+      <c r="J34" s="20" t="n">
         <v>4.49</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n">
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="11" t="n">
         <v>1.8</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" s="11" t="n">
         <v>0.88</v>
       </c>
-      <c r="J35" s="8" t="n"/>
+      <c r="J35" s="11" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n">
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="n">
         <v>52.4</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="11" t="n">
         <v>3.1</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="11" t="n">
         <v>-0.95</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="I36" s="11" t="n">
         <v>3.92</v>
       </c>
-      <c r="J36" s="8" t="n">
+      <c r="J36" s="11" t="n">
         <v>2.39</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>San Jose</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="n">
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="n">
         <v>44.6</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="14" t="n">
         <v>4.1</v>
       </c>
-      <c r="H37" s="11" t="n">
+      <c r="H37" s="14" t="n">
         <v>-0.48</v>
       </c>
-      <c r="I37" s="11" t="n">
+      <c r="I37" s="14" t="n">
         <v>-0.78</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J37" s="14" t="n">
         <v>7.4</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="n">
         <v>37.8</v>
       </c>
-      <c r="G38" s="17" t="n">
+      <c r="G38" s="20" t="n">
         <v>3.9</v>
       </c>
-      <c r="H38" s="17" t="n">
+      <c r="H38" s="20" t="n">
         <v>-0.91</v>
       </c>
-      <c r="I38" s="17" t="n">
+      <c r="I38" s="20" t="n">
         <v>5.51</v>
       </c>
-      <c r="J38" s="17" t="n">
+      <c r="J38" s="20" t="n">
         <v>2.47</v>
       </c>
     </row>
@@ -7810,78 +7810,78 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Providence-Warwick</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="n">
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="n">
         <v>44.3</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H40" s="11" t="n">
+      <c r="H40" s="14" t="n">
         <v>1.69</v>
       </c>
-      <c r="I40" s="11" t="n">
+      <c r="I40" s="14" t="n">
         <v>3.09</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="J40" s="14" t="n">
         <v>7.47</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n">
+      <c r="A41" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee-Waukesha</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="n">
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="n">
         <v>39.2</v>
       </c>
-      <c r="G41" s="14" t="n">
+      <c r="G41" s="17" t="n">
         <v>3.8</v>
       </c>
-      <c r="H41" s="14" t="n">
+      <c r="H41" s="17" t="n">
         <v>0.85</v>
       </c>
-      <c r="I41" s="14" t="n">
+      <c r="I41" s="17" t="n">
         <v>0.52</v>
       </c>
-      <c r="J41" s="14" t="n">
+      <c r="J41" s="17" t="n">
         <v>5.18</v>
       </c>
     </row>
@@ -7924,154 +7924,154 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="n">
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
         <v>44.2</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H43" s="14" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="14" t="n">
         <v>4.2</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="J43" s="14" t="n">
         <v>1.67</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n">
+      <c r="A44" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>Louisville-Jefferson County</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Louisville</t>
         </is>
       </c>
-      <c r="D44" s="20" t="n">
+      <c r="D44" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
         <is>
           <t>C-</t>
         </is>
       </c>
-      <c r="F44" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J44" s="20" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
+      <c r="F45" s="20" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I45" s="20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J45" s="20" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F45" s="17" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H45" s="17" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="I45" s="17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J45" s="17" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="n">
+      <c r="F46" s="17" t="n">
         <v>40.1</v>
       </c>
-      <c r="G46" s="14" t="n">
+      <c r="G46" s="17" t="n">
         <v>4.7</v>
       </c>
-      <c r="H46" s="14" t="n">
+      <c r="H46" s="17" t="n">
         <v>-0.92</v>
       </c>
-      <c r="I46" s="14" t="n">
+      <c r="I46" s="17" t="n">
         <v>4.52</v>
       </c>
-      <c r="J46" s="14" t="n">
+      <c r="J46" s="17" t="n">
         <v>0.86</v>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -8114,40 +8114,40 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n">
+      <c r="A48" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="n">
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
         <v>45.6</v>
       </c>
-      <c r="G48" s="11" t="n">
+      <c r="G48" s="14" t="n">
         <v>3.5</v>
       </c>
-      <c r="H48" s="11" t="n">
+      <c r="H48" s="14" t="n">
         <v>-1.1</v>
       </c>
-      <c r="I48" s="11" t="n">
+      <c r="I48" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="J48" s="14" t="n">
         <v>3.04</v>
       </c>
     </row>
@@ -8190,78 +8190,78 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="n">
+      <c r="A50" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>Grand Rapids</t>
         </is>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="n">
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="n">
         <v>32.1</v>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="G50" s="20" t="n">
         <v>4.3</v>
       </c>
-      <c r="H50" s="17" t="n">
+      <c r="H50" s="20" t="n">
         <v>-7.49</v>
       </c>
-      <c r="I50" s="17" t="n">
+      <c r="I50" s="20" t="n">
         <v>1.41</v>
       </c>
-      <c r="J50" s="17" t="n">
+      <c r="J50" s="20" t="n">
         <v>4.59</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Hartford</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
         <v>67.7</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="5" t="n">
         <v>2.77</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I51" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="5" t="n">
         <v>3.12</v>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" s="37" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" s="37" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E6" s="37" t="n">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" s="37" t="n">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E8" s="37" t="n">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="H8" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E9" s="37" t="n">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E10" s="37" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="H10" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E11" s="37" t="n">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="H11" s="37" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E12" s="37" t="n">

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
@@ -821,33 +821,33 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="A7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte-Concord-Gastonia</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D27" s="19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="17" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F32" s="17" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F35" s="20" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="23" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F42" s="23" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F47" s="23" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>84</v>
       </c>
       <c r="K2" s="32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -2375,7 +2375,7 @@
         <v>36</v>
       </c>
       <c r="K3" s="32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -2410,7 +2410,7 @@
         <v>66</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -2445,77 +2445,77 @@
         <v>86</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B6" s="29" t="n">
         <v>68</v>
       </c>
-      <c r="C6" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="D6" s="32" t="n">
-        <v>40</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>62</v>
+      <c r="C6" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H6" s="33" t="n"/>
       <c r="I6" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="J6" s="32" t="n">
-        <v>12</v>
+        <v>80</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>68</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>46</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H7" s="33" t="n"/>
       <c r="I7" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="J7" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="K7" s="32" t="n">
-        <v>20</v>
+        <v>96</v>
+      </c>
+      <c r="J7" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" s="33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2655,7 +2655,7 @@
         <v>20</v>
       </c>
       <c r="K11" s="32" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -2690,7 +2690,7 @@
         <v>40</v>
       </c>
       <c r="K12" s="32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2725,7 +2725,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2795,7 +2795,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -2829,8 +2829,8 @@
       <c r="J16" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="K16" s="30" t="n">
-        <v>70</v>
+      <c r="K16" s="31" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="17">
@@ -2865,7 +2865,7 @@
         <v>30</v>
       </c>
       <c r="K17" s="31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -2900,7 +2900,7 @@
         <v>78</v>
       </c>
       <c r="K18" s="32" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -2934,8 +2934,8 @@
       <c r="J19" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K19" s="31" t="n">
-        <v>50</v>
+      <c r="K19" s="32" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2970,7 +2970,7 @@
         <v>26</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -3005,7 +3005,7 @@
         <v>62</v>
       </c>
       <c r="K21" s="32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
@@ -3040,7 +3040,7 @@
         <v>76</v>
       </c>
       <c r="K22" s="31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -3075,7 +3075,7 @@
         <v>48</v>
       </c>
       <c r="K23" s="31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
@@ -3110,7 +3110,7 @@
         <v>18</v>
       </c>
       <c r="K24" s="32" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="32" t="n">
         <v>18</v>
@@ -3215,7 +3215,7 @@
         <v>44</v>
       </c>
       <c r="K27" s="32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -3250,7 +3250,7 @@
         <v>92</v>
       </c>
       <c r="K28" s="32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
@@ -3285,7 +3285,7 @@
         <v>60</v>
       </c>
       <c r="K29" s="31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
@@ -3320,7 +3320,7 @@
         <v>56</v>
       </c>
       <c r="K30" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
@@ -3390,7 +3390,7 @@
         <v>90</v>
       </c>
       <c r="K32" s="32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -3495,7 +3495,7 @@
         <v>28</v>
       </c>
       <c r="K35" s="32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -3530,7 +3530,7 @@
         <v>82</v>
       </c>
       <c r="K36" s="32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B41" s="29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="32" t="n">
         <v>12</v>
@@ -3705,7 +3705,7 @@
         <v>16</v>
       </c>
       <c r="K41" s="32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42">
@@ -3740,7 +3740,7 @@
         <v>14</v>
       </c>
       <c r="K42" s="31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
@@ -3845,7 +3845,7 @@
         <v>32</v>
       </c>
       <c r="K45" s="32" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
@@ -3915,7 +3915,7 @@
         <v>54</v>
       </c>
       <c r="K47" s="31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -4329,7 +4329,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
@@ -4338,79 +4338,75 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>-1.49</v>
+        <v>0.64</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>4.22</v>
+        <v>5.08</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>1.42</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="H6" s="33" t="n"/>
       <c r="I6" s="33" t="n">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="J6" s="33" t="n">
-        <v>-22.75</v>
+        <v>2.5</v>
       </c>
       <c r="K6" s="33" t="n">
-        <v>6.72</v>
+        <v>6.87</v>
       </c>
       <c r="L6" s="33" t="n">
-        <v>10.34</v>
+        <v>1.27</v>
       </c>
       <c r="M6" s="33" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>68 (A)</t>
+          <t>67 (A-)</t>
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.64</v>
+        <v>-1.49</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>5.08</v>
+        <v>4.22</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.89</v>
+        <v>1.42</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>4.4</v>
+        <v>3.66</v>
       </c>
       <c r="H7" s="33" t="n"/>
       <c r="I7" s="33" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>2.5</v>
+        <v>-22.75</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="L7" s="33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M7" s="33" t="n">
-        <v>80</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L7" s="33" t="n"/>
+      <c r="M7" s="33" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5235,7 +5231,7 @@
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>49 (C+)</t>
+          <t>48 (C+)</t>
         </is>
       </c>
       <c r="C27" s="33" t="n">
@@ -5837,7 +5833,7 @@
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>37 (C-)</t>
+          <t>36 (C-)</t>
         </is>
       </c>
       <c r="C41" s="33" t="n">
@@ -6441,7 +6437,7 @@
         </is>
       </c>
       <c r="F3" s="14" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>4.8</v>
@@ -6479,7 +6475,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="G4" s="26" t="n">
         <v>5.2</v>
@@ -6517,7 +6513,7 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>4.4</v>
@@ -6547,7 +6543,7 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
@@ -6821,7 +6817,7 @@
         </is>
       </c>
       <c r="F13" s="23" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>5.9</v>
@@ -7079,7 +7075,7 @@
         </is>
       </c>
       <c r="D20" s="23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
@@ -7087,7 +7083,7 @@
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>4.6</v>
@@ -7125,7 +7121,7 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>4.6</v>
@@ -7155,7 +7151,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
@@ -7163,7 +7159,7 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>68</v>
+        <v>67.2</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>3.7</v>
@@ -7239,7 +7235,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>3.9</v>
@@ -7293,40 +7289,40 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="n">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="5" t="n">
         <v>0.64</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="5" t="n">
         <v>5.08</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="5" t="n">
         <v>0.89</v>
       </c>
     </row>
@@ -7353,7 +7349,7 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>4.9</v>
@@ -7391,7 +7387,7 @@
         </is>
       </c>
       <c r="F28" s="20" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>5.2</v>
@@ -7467,7 +7463,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>4.8</v>
@@ -7543,7 +7539,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>3.9</v>
@@ -7693,7 +7689,7 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>3.2</v>
@@ -7769,7 +7765,7 @@
         </is>
       </c>
       <c r="F38" s="20" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>3.7</v>
@@ -7807,7 +7803,7 @@
         </is>
       </c>
       <c r="F39" s="23" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="G39" s="23" t="n">
         <v>4.8</v>
@@ -7959,7 +7955,7 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="G43" s="17" t="n">
         <v>3.9</v>
@@ -8111,7 +8107,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.7</v>
@@ -8149,7 +8145,7 @@
         </is>
       </c>
       <c r="F48" s="17" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="G48" s="17" t="n">
         <v>3.4</v>
@@ -8498,7 +8494,7 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C7" s="39" t="n">
@@ -8532,15 +8528,15 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E8" s="40" t="n">
